--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>24753</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>2.4300000667572</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>2.48000001907349</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>21359</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>2.47000002861023</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -62917,7 +62917,7 @@
         <v>21359</v>
       </c>
       <c r="C2720" t="n">
-        <v>2.46000003814697</v>
+        <v>2.47000002861023</v>
       </c>
       <c r="D2720" t="n">
         <v>2.38000011444092</v>
@@ -62929,6 +62929,29 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>5234</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>2.41000008583069</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>2.41000008583069</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>2305</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>7320</v>
+        <v>6328</v>
       </c>
       <c r="C2715" t="n">
-        <v>2.58999991416931</v>
+        <v>2.63000011444092</v>
       </c>
       <c r="D2715" t="n">
-        <v>2.53999996185303</v>
+        <v>2.5699999332428</v>
       </c>
       <c r="E2715" t="n">
-        <v>2.55999994277954</v>
+        <v>2.61999988555908</v>
       </c>
       <c r="F2715" t="n">
-        <v>2.57999992370605</v>
+        <v>2.61999988555908</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>9134</v>
+        <v>7320</v>
       </c>
       <c r="C2716" t="n">
-        <v>2.54999995231628</v>
+        <v>2.58999991416931</v>
       </c>
       <c r="D2716" t="n">
-        <v>2.50999999046326</v>
+        <v>2.53999996185303</v>
       </c>
       <c r="E2716" t="n">
-        <v>2.51999998092651</v>
+        <v>2.55999994277954</v>
       </c>
       <c r="F2716" t="n">
-        <v>2.53999996185303</v>
+        <v>2.57999992370605</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>13904</v>
+        <v>9134</v>
       </c>
       <c r="C2717" t="n">
-        <v>2.52999997138977</v>
+        <v>2.54999995231628</v>
       </c>
       <c r="D2717" t="n">
-        <v>2.49000000953674</v>
+        <v>2.50999999046326</v>
       </c>
       <c r="E2717" t="n">
-        <v>2.50999999046326</v>
+        <v>2.51999998092651</v>
       </c>
       <c r="F2717" t="n">
-        <v>2.52999997138977</v>
+        <v>2.53999996185303</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>10513</v>
+        <v>13904</v>
       </c>
       <c r="C2718" t="n">
-        <v>2.5</v>
+        <v>2.52999997138977</v>
       </c>
       <c r="D2718" t="n">
-        <v>2.46000003814697</v>
+        <v>2.49000000953674</v>
       </c>
       <c r="E2718" t="n">
-        <v>2.5</v>
+        <v>2.50999999046326</v>
       </c>
       <c r="F2718" t="n">
-        <v>2.49000000953674</v>
+        <v>2.52999997138977</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>24753</v>
+        <v>10513</v>
       </c>
       <c r="C2719" t="n">
-        <v>2.48000001907349</v>
+        <v>2.5</v>
       </c>
       <c r="D2719" t="n">
-        <v>2.4300000667572</v>
+        <v>2.46000003814697</v>
       </c>
       <c r="E2719" t="n">
-        <v>2.48000001907349</v>
+        <v>2.5</v>
       </c>
       <c r="F2719" t="n">
-        <v>2.46000003814697</v>
+        <v>2.49000000953674</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>21359</v>
+        <v>24753</v>
       </c>
       <c r="C2720" t="n">
-        <v>2.47000002861023</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="D2720" t="n">
-        <v>2.38000011444092</v>
+        <v>2.4300000667572</v>
       </c>
       <c r="E2720" t="n">
-        <v>2.42000007629395</v>
+        <v>2.48000001907349</v>
       </c>
       <c r="F2720" t="n">
-        <v>2.47000002861023</v>
+        <v>2.46000003814697</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>5234</v>
+        <v>21359</v>
       </c>
       <c r="C2721" t="n">
-        <v>2.46000003814697</v>
+        <v>2.47000002861023</v>
       </c>
       <c r="D2721" t="n">
-        <v>2.41000008583069</v>
+        <v>2.38000011444092</v>
       </c>
       <c r="E2721" t="n">
-        <v>2.41000008583069</v>
+        <v>2.42000007629395</v>
       </c>
       <c r="F2721" t="n">
-        <v>2.46000003814697</v>
+        <v>2.47000002861023</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>2305</v>
+        <v>5234</v>
       </c>
       <c r="C2722" t="n">
         <v>2.46000003814697</v>
       </c>
       <c r="D2722" t="n">
-        <v>2.45000004768372</v>
+        <v>2.41000008583069</v>
       </c>
       <c r="E2722" t="n">
-        <v>2.46000003814697</v>
+        <v>2.41000008583069</v>
       </c>
       <c r="F2722" t="n">
         <v>2.46000003814697</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>3499</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>2.45000004768372</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>2.46000003814697</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>2.42000007629395</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>2.4300000667572</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>2719</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>2.44000005722046</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>2.40000009536743</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>2.41000008583069</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>9227</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>2.42000007629395</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>2.41000008583069</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>2.41000008583069</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>2.42000007629395</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>443</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>2.39000010490417</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>2.39000010490417</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>6994</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>2.41000008583069</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>2.35999989509583</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>2.39000010490417</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>30028</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>2.4300000667572</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>2.41000008583069</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PQ.MI.xlsx
+++ b/data/PQ.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.34700000286102</v>
       </c>
       <c r="G2" t="n">
-        <v>0.919120013713837</v>
+        <v>0.919120311737061</v>
       </c>
       <c r="H2" t="n">
         <v>13729</v>
@@ -456,7 +456,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G3" t="n">
-        <v>0.947096288204193</v>
+        <v>0.947096407413483</v>
       </c>
       <c r="H3" t="n">
         <v>24923</v>
@@ -485,7 +485,7 @@
         <v>1.36800003051758</v>
       </c>
       <c r="G4" t="n">
-        <v>0.933449506759644</v>
+        <v>0.933449447154999</v>
       </c>
       <c r="H4" t="n">
         <v>8741</v>
@@ -514,7 +514,7 @@
         <v>1.36500000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>0.931402444839478</v>
+        <v>0.931402385234833</v>
       </c>
       <c r="H5" t="n">
         <v>15275</v>
@@ -543,7 +543,7 @@
         <v>1.32700002193451</v>
       </c>
       <c r="G6" t="n">
-        <v>0.905473291873932</v>
+        <v>0.905473351478577</v>
       </c>
       <c r="H6" t="n">
         <v>16873</v>
@@ -630,7 +630,7 @@
         <v>1.3400000333786</v>
       </c>
       <c r="G9" t="n">
-        <v>0.91434383392334</v>
+        <v>0.914343774318695</v>
       </c>
       <c r="H9" t="n">
         <v>8350</v>
@@ -659,7 +659,7 @@
         <v>1.317999958992</v>
       </c>
       <c r="G10" t="n">
-        <v>0.899331986904144</v>
+        <v>0.899332106113434</v>
       </c>
       <c r="H10" t="n">
         <v>21935</v>
@@ -717,7 +717,7 @@
         <v>1.2039999961853</v>
       </c>
       <c r="G12" t="n">
-        <v>0.821544826030731</v>
+        <v>0.821544706821442</v>
       </c>
       <c r="H12" t="n">
         <v>26168</v>
@@ -746,7 +746,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G13" t="n">
-        <v>0.832462310791016</v>
+        <v>0.832462191581726</v>
       </c>
       <c r="H13" t="n">
         <v>42418</v>
@@ -775,7 +775,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G14" t="n">
-        <v>0.808580100536346</v>
+        <v>0.808580160140991</v>
       </c>
       <c r="H14" t="n">
         <v>33578</v>
@@ -804,7 +804,7 @@
         <v>1.25699996948242</v>
       </c>
       <c r="G15" t="n">
-        <v>0.857708990573883</v>
+        <v>0.857709050178528</v>
       </c>
       <c r="H15" t="n">
         <v>74278</v>
@@ -833,7 +833,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G16" t="n">
-        <v>0.835874021053314</v>
+        <v>0.835874080657959</v>
       </c>
       <c r="H16" t="n">
         <v>8710</v>
@@ -891,7 +891,7 @@
         <v>1.25899994373322</v>
       </c>
       <c r="G18" t="n">
-        <v>0.85907369852066</v>
+        <v>0.85907381772995</v>
       </c>
       <c r="H18" t="n">
         <v>9061</v>
@@ -920,7 +920,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G19" t="n">
-        <v>0.856344282627106</v>
+        <v>0.856344401836395</v>
       </c>
       <c r="H19" t="n">
         <v>3523</v>
@@ -949,7 +949,7 @@
         <v>1.21599996089935</v>
       </c>
       <c r="G20" t="n">
-        <v>0.829732894897461</v>
+        <v>0.829732835292816</v>
       </c>
       <c r="H20" t="n">
         <v>9051</v>
@@ -1007,7 +1007,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G22" t="n">
-        <v>0.824956595897675</v>
+        <v>0.82495653629303</v>
       </c>
       <c r="H22" t="n">
         <v>29929</v>
@@ -1036,7 +1036,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G23" t="n">
-        <v>0.808580100536346</v>
+        <v>0.808580160140991</v>
       </c>
       <c r="H23" t="n">
         <v>10106</v>
@@ -1065,7 +1065,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G24" t="n">
-        <v>0.791521370410919</v>
+        <v>0.791521489620209</v>
       </c>
       <c r="H24" t="n">
         <v>7789</v>
@@ -1094,7 +1094,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G25" t="n">
-        <v>0.781286239624023</v>
+        <v>0.781286299228668</v>
       </c>
       <c r="H25" t="n">
         <v>21051</v>
@@ -1152,7 +1152,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G27" t="n">
-        <v>0.709640026092529</v>
+        <v>0.70963990688324</v>
       </c>
       <c r="H27" t="n">
         <v>43551</v>
@@ -1181,7 +1181,7 @@
         <v>0.995000004768372</v>
       </c>
       <c r="G28" t="n">
-        <v>0.678934395313263</v>
+        <v>0.678934335708618</v>
       </c>
       <c r="H28" t="n">
         <v>27106</v>
@@ -1210,7 +1210,7 @@
         <v>1.01999998092651</v>
       </c>
       <c r="G29" t="n">
-        <v>0.695993006229401</v>
+        <v>0.695993065834045</v>
       </c>
       <c r="H29" t="n">
         <v>39148</v>
@@ -1239,7 +1239,7 @@
         <v>0.982500016689301</v>
       </c>
       <c r="G30" t="n">
-        <v>0.670405089855194</v>
+        <v>0.670405030250549</v>
       </c>
       <c r="H30" t="n">
         <v>34091</v>
@@ -1268,7 +1268,7 @@
         <v>1.00999999046326</v>
       </c>
       <c r="G31" t="n">
-        <v>0.689169585704803</v>
+        <v>0.689169526100159</v>
       </c>
       <c r="H31" t="n">
         <v>17375</v>
@@ -1297,7 +1297,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G32" t="n">
-        <v>0.736933767795563</v>
+        <v>0.736933827400208</v>
       </c>
       <c r="H32" t="n">
         <v>62693</v>
@@ -1326,7 +1326,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G33" t="n">
-        <v>0.750580728054047</v>
+        <v>0.750580668449402</v>
       </c>
       <c r="H33" t="n">
         <v>17442</v>
@@ -1413,7 +1413,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G36" t="n">
-        <v>0.764227628707886</v>
+        <v>0.764227688312531</v>
       </c>
       <c r="H36" t="n">
         <v>4111</v>
@@ -1442,7 +1442,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G37" t="n">
-        <v>0.784698069095612</v>
+        <v>0.784697949886322</v>
       </c>
       <c r="H37" t="n">
         <v>17840</v>
@@ -1500,7 +1500,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G39" t="n">
-        <v>0.78810977935791</v>
+        <v>0.788109600543976</v>
       </c>
       <c r="H39" t="n">
         <v>5789</v>
@@ -1529,7 +1529,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G40" t="n">
-        <v>0.766274809837341</v>
+        <v>0.766274750232697</v>
       </c>
       <c r="H40" t="n">
         <v>5533</v>
@@ -1558,7 +1558,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G41" t="n">
-        <v>0.794933140277863</v>
+        <v>0.794933199882507</v>
       </c>
       <c r="H41" t="n">
         <v>2470</v>
@@ -1616,7 +1616,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G43" t="n">
-        <v>0.798344910144806</v>
+        <v>0.798344850540161</v>
       </c>
       <c r="H43" t="n">
         <v>10710</v>
@@ -1645,7 +1645,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G44" t="n">
-        <v>0.808580100536346</v>
+        <v>0.808580160140991</v>
       </c>
       <c r="H44" t="n">
         <v>12054</v>
@@ -1732,7 +1732,7 @@
         <v>1.1710000038147</v>
       </c>
       <c r="G47" t="n">
-        <v>0.79902720451355</v>
+        <v>0.799027264118195</v>
       </c>
       <c r="H47" t="n">
         <v>47261</v>
@@ -1761,7 +1761,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G48" t="n">
-        <v>0.809944868087769</v>
+        <v>0.809944927692413</v>
       </c>
       <c r="H48" t="n">
         <v>21238</v>
@@ -1790,7 +1790,7 @@
         <v>1.21800005435944</v>
       </c>
       <c r="G49" t="n">
-        <v>0.831097602844238</v>
+        <v>0.831097662448883</v>
       </c>
       <c r="H49" t="n">
         <v>6874</v>
@@ -1819,7 +1819,7 @@
         <v>1.22399997711182</v>
       </c>
       <c r="G50" t="n">
-        <v>0.835191667079926</v>
+        <v>0.835191607475281</v>
       </c>
       <c r="H50" t="n">
         <v>26742</v>
@@ -1848,7 +1848,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G51" t="n">
-        <v>0.84610915184021</v>
+        <v>0.846109211444855</v>
       </c>
       <c r="H51" t="n">
         <v>16335</v>
@@ -1906,7 +1906,7 @@
         <v>1.24500000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>0.849520862102509</v>
+        <v>0.849520981311798</v>
       </c>
       <c r="H53" t="n">
         <v>9600</v>
@@ -1964,7 +1964,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G55" t="n">
-        <v>0.842697441577911</v>
+        <v>0.842697381973267</v>
       </c>
       <c r="H55" t="n">
         <v>39486</v>
@@ -1993,7 +1993,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G56" t="n">
-        <v>0.811991989612579</v>
+        <v>0.81199187040329</v>
       </c>
       <c r="H56" t="n">
         <v>48179</v>
@@ -2022,7 +2022,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G57" t="n">
-        <v>0.829050660133362</v>
+        <v>0.829050421714783</v>
       </c>
       <c r="H57" t="n">
         <v>2413</v>
@@ -2051,7 +2051,7 @@
         <v>1.2150000333786</v>
       </c>
       <c r="G58" t="n">
-        <v>0.829050660133362</v>
+        <v>0.829050421714783</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>1.20899999141693</v>
       </c>
       <c r="G60" t="n">
-        <v>0.824956595897675</v>
+        <v>0.82495653629303</v>
       </c>
       <c r="H60" t="n">
         <v>964</v>
@@ -2138,7 +2138,7 @@
         <v>1.19000005722046</v>
       </c>
       <c r="G61" t="n">
-        <v>0.811991989612579</v>
+        <v>0.81199187040329</v>
       </c>
       <c r="H61" t="n">
         <v>3100</v>
@@ -2167,7 +2167,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>0.832462310791016</v>
+        <v>0.832462191581726</v>
       </c>
       <c r="H62" t="n">
         <v>1061</v>
@@ -2196,7 +2196,7 @@
         <v>1.22899997234344</v>
       </c>
       <c r="G63" t="n">
-        <v>0.838603317737579</v>
+        <v>0.838603496551514</v>
       </c>
       <c r="H63" t="n">
         <v>2781</v>
@@ -2225,7 +2225,7 @@
         <v>1.22000002861023</v>
       </c>
       <c r="G64" t="n">
-        <v>0.832462310791016</v>
+        <v>0.832462191581726</v>
       </c>
       <c r="H64" t="n">
         <v>11362</v>
@@ -2254,7 +2254,7 @@
         <v>1.20000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>0.818815410137177</v>
+        <v>0.818815350532532</v>
       </c>
       <c r="H65" t="n">
         <v>1200</v>
@@ -2283,7 +2283,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G66" t="n">
-        <v>0.784698069095612</v>
+        <v>0.784697949886322</v>
       </c>
       <c r="H66" t="n">
         <v>10360</v>
@@ -2341,7 +2341,7 @@
         <v>1.15499997138977</v>
       </c>
       <c r="G68" t="n">
-        <v>0.78810977935791</v>
+        <v>0.788109600543976</v>
       </c>
       <c r="H68" t="n">
         <v>4100</v>
@@ -2370,7 +2370,7 @@
         <v>1.19799995422363</v>
       </c>
       <c r="G69" t="n">
-        <v>0.81745058298111</v>
+        <v>0.817450702190399</v>
       </c>
       <c r="H69" t="n">
         <v>2151</v>
@@ -2399,7 +2399,7 @@
         <v>1.192999958992</v>
       </c>
       <c r="G70" t="n">
-        <v>0.814038872718811</v>
+        <v>0.814038932323456</v>
       </c>
       <c r="H70" t="n">
         <v>1100</v>
@@ -2428,7 +2428,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G71" t="n">
-        <v>0.798344910144806</v>
+        <v>0.798344850540161</v>
       </c>
       <c r="H71" t="n">
         <v>3950</v>
@@ -2457,7 +2457,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G72" t="n">
-        <v>0.791521370410919</v>
+        <v>0.791521489620209</v>
       </c>
       <c r="H72" t="n">
         <v>13908</v>
@@ -2515,7 +2515,7 @@
         <v>1.19900000095367</v>
       </c>
       <c r="G74" t="n">
-        <v>0.818133056163788</v>
+        <v>0.818132996559143</v>
       </c>
       <c r="H74" t="n">
         <v>18069</v>
@@ -2573,7 +2573,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G76" t="n">
-        <v>0.798344910144806</v>
+        <v>0.798344850540161</v>
       </c>
       <c r="H76" t="n">
         <v>6535</v>
@@ -2660,7 +2660,7 @@
         <v>1.18499994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>0.808580100536346</v>
+        <v>0.808580160140991</v>
       </c>
       <c r="H79" t="n">
         <v>1626</v>
@@ -2747,7 +2747,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G82" t="n">
-        <v>0.809944868087769</v>
+        <v>0.809944927692413</v>
       </c>
       <c r="H82" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G84" t="n">
-        <v>0.786745011806488</v>
+        <v>0.786745071411133</v>
       </c>
       <c r="H84" t="n">
         <v>8847</v>
@@ -2834,7 +2834,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G85" t="n">
-        <v>0.791521370410919</v>
+        <v>0.791521489620209</v>
       </c>
       <c r="H85" t="n">
         <v>2860</v>
@@ -2863,7 +2863,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G86" t="n">
-        <v>0.784698069095612</v>
+        <v>0.784697949886322</v>
       </c>
       <c r="H86" t="n">
         <v>16058</v>
@@ -2892,7 +2892,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G87" t="n">
-        <v>0.784698069095612</v>
+        <v>0.784697949886322</v>
       </c>
       <c r="H87" t="n">
         <v>5780</v>
@@ -2921,7 +2921,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>0.760815918445587</v>
+        <v>0.760815978050232</v>
       </c>
       <c r="H88" t="n">
         <v>32038</v>
@@ -2950,7 +2950,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G89" t="n">
-        <v>0.751945376396179</v>
+        <v>0.751945436000824</v>
       </c>
       <c r="H89" t="n">
         <v>21394</v>
@@ -2979,7 +2979,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>0.774462819099426</v>
+        <v>0.774462759494781</v>
       </c>
       <c r="H90" t="n">
         <v>377</v>
@@ -3095,7 +3095,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G94" t="n">
-        <v>0.750580728054047</v>
+        <v>0.750580668449402</v>
       </c>
       <c r="H94" t="n">
         <v>2800</v>
@@ -3124,7 +3124,7 @@
         <v>1.13499999046326</v>
       </c>
       <c r="G95" t="n">
-        <v>0.774462819099426</v>
+        <v>0.774462759494781</v>
       </c>
       <c r="H95" t="n">
         <v>5088</v>
@@ -3182,7 +3182,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G97" t="n">
-        <v>0.764227628707886</v>
+        <v>0.764227688312531</v>
       </c>
       <c r="H97" t="n">
         <v>2288</v>
@@ -3211,7 +3211,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G98" t="n">
-        <v>0.784698069095612</v>
+        <v>0.784697949886322</v>
       </c>
       <c r="H98" t="n">
         <v>8686</v>
@@ -3240,7 +3240,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G99" t="n">
-        <v>0.77787458896637</v>
+        <v>0.777874529361725</v>
       </c>
       <c r="H99" t="n">
         <v>6874</v>
@@ -3269,7 +3269,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G100" t="n">
-        <v>0.791521370410919</v>
+        <v>0.791521489620209</v>
       </c>
       <c r="H100" t="n">
         <v>1126</v>
@@ -3298,7 +3298,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G101" t="n">
-        <v>0.764227628707886</v>
+        <v>0.764227688312531</v>
       </c>
       <c r="H101" t="n">
         <v>8381</v>
@@ -3327,7 +3327,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G102" t="n">
-        <v>0.797662556171417</v>
+        <v>0.797662675380707</v>
       </c>
       <c r="H102" t="n">
         <v>23764</v>
@@ -3385,7 +3385,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G104" t="n">
-        <v>0.784698069095612</v>
+        <v>0.784697949886322</v>
       </c>
       <c r="H104" t="n">
         <v>899</v>
@@ -3472,7 +3472,7 @@
         <v>1.18700003623962</v>
       </c>
       <c r="G107" t="n">
-        <v>0.809944868087769</v>
+        <v>0.809944927692413</v>
       </c>
       <c r="H107" t="n">
         <v>9157</v>
@@ -3501,7 +3501,7 @@
         <v>1.16999995708466</v>
       </c>
       <c r="G108" t="n">
-        <v>0.798344910144806</v>
+        <v>0.798344850540161</v>
       </c>
       <c r="H108" t="n">
         <v>15692</v>
@@ -3530,7 +3530,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G109" t="n">
-        <v>0.791521370410919</v>
+        <v>0.791521489620209</v>
       </c>
       <c r="H109" t="n">
         <v>5026</v>
@@ -3559,7 +3559,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G110" t="n">
-        <v>0.77787458896637</v>
+        <v>0.777874529361725</v>
       </c>
       <c r="H110" t="n">
         <v>7531</v>
@@ -3588,7 +3588,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G111" t="n">
-        <v>0.77787458896637</v>
+        <v>0.777874529361725</v>
       </c>
       <c r="H111" t="n">
         <v>990</v>
@@ -3617,7 +3617,7 @@
         <v>1.13199996948242</v>
       </c>
       <c r="G112" t="n">
-        <v>0.772415697574615</v>
+        <v>0.772415816783905</v>
       </c>
       <c r="H112" t="n">
         <v>97125</v>
@@ -3646,7 +3646,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G113" t="n">
-        <v>0.784698069095612</v>
+        <v>0.784697949886322</v>
       </c>
       <c r="H113" t="n">
         <v>23237</v>
@@ -3704,7 +3704,7 @@
         <v>1.10800004005432</v>
       </c>
       <c r="G115" t="n">
-        <v>0.756039559841156</v>
+        <v>0.756039440631866</v>
       </c>
       <c r="H115" t="n">
         <v>49151</v>
@@ -3733,7 +3733,7 @@
         <v>1.09800004959106</v>
       </c>
       <c r="G116" t="n">
-        <v>0.749216079711914</v>
+        <v>0.749216139316559</v>
       </c>
       <c r="H116" t="n">
         <v>27800</v>
@@ -3791,7 +3791,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G118" t="n">
-        <v>0.784698069095612</v>
+        <v>0.784697949886322</v>
       </c>
       <c r="H118" t="n">
         <v>21280</v>
@@ -3849,7 +3849,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G120" t="n">
-        <v>0.781286239624023</v>
+        <v>0.781286299228668</v>
       </c>
       <c r="H120" t="n">
         <v>2030</v>
@@ -3878,7 +3878,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G121" t="n">
-        <v>0.77787458896637</v>
+        <v>0.777874529361725</v>
       </c>
       <c r="H121" t="n">
         <v>8600</v>
@@ -3907,7 +3907,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G122" t="n">
-        <v>0.764227628707886</v>
+        <v>0.764227688312531</v>
       </c>
       <c r="H122" t="n">
         <v>10482</v>
@@ -3936,7 +3936,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G123" t="n">
-        <v>0.776509881019592</v>
+        <v>0.776509821414948</v>
       </c>
       <c r="H123" t="n">
         <v>11307</v>
@@ -4023,7 +4023,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G126" t="n">
-        <v>0.723286807537079</v>
+        <v>0.723286867141724</v>
       </c>
       <c r="H126" t="n">
         <v>37720</v>
@@ -4052,7 +4052,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G127" t="n">
-        <v>0.726016283035278</v>
+        <v>0.726016223430634</v>
       </c>
       <c r="H127" t="n">
         <v>11730</v>
@@ -4081,7 +4081,7 @@
         <v>1.06400001049042</v>
       </c>
       <c r="G128" t="n">
-        <v>0.726016283035278</v>
+        <v>0.726016223430634</v>
       </c>
       <c r="H128" t="n">
         <v>5165</v>
@@ -4197,7 +4197,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G132" t="n">
-        <v>0.709640026092529</v>
+        <v>0.70963990688324</v>
       </c>
       <c r="H132" t="n">
         <v>18775</v>
@@ -4226,7 +4226,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G133" t="n">
-        <v>0.709640026092529</v>
+        <v>0.70963990688324</v>
       </c>
       <c r="H133" t="n">
         <v>13398</v>
@@ -4255,7 +4255,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G134" t="n">
-        <v>0.709640026092529</v>
+        <v>0.70963990688324</v>
       </c>
       <c r="H134" t="n">
         <v>16368</v>
@@ -4313,7 +4313,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G136" t="n">
-        <v>0.741710245609283</v>
+        <v>0.741710305213928</v>
       </c>
       <c r="H136" t="n">
         <v>38633</v>
@@ -4342,7 +4342,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G137" t="n">
-        <v>0.723286807537079</v>
+        <v>0.723286867141724</v>
       </c>
       <c r="H137" t="n">
         <v>19819</v>
@@ -4371,7 +4371,7 @@
         <v>1.06500005722046</v>
       </c>
       <c r="G138" t="n">
-        <v>0.726698756217957</v>
+        <v>0.726698637008667</v>
       </c>
       <c r="H138" t="n">
         <v>15169</v>
@@ -4400,7 +4400,7 @@
         <v>1.07099997997284</v>
       </c>
       <c r="G139" t="n">
-        <v>0.730792701244354</v>
+        <v>0.730792641639709</v>
       </c>
       <c r="H139" t="n">
         <v>1134</v>
@@ -4487,7 +4487,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G142" t="n">
-        <v>0.73829859495163</v>
+        <v>0.73829847574234</v>
       </c>
       <c r="H142" t="n">
         <v>26078</v>
@@ -4516,7 +4516,7 @@
         <v>1.11000001430511</v>
       </c>
       <c r="G143" t="n">
-        <v>0.757404208183289</v>
+        <v>0.757404148578644</v>
       </c>
       <c r="H143" t="n">
         <v>3211</v>
@@ -4603,7 +4603,7 @@
         <v>1.12000000476837</v>
       </c>
       <c r="G146" t="n">
-        <v>0.764227628707886</v>
+        <v>0.764227688312531</v>
       </c>
       <c r="H146" t="n">
         <v>13197</v>
@@ -4632,7 +4632,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G147" t="n">
-        <v>0.781286239624023</v>
+        <v>0.781286299228668</v>
       </c>
       <c r="H147" t="n">
         <v>54859</v>
@@ -4690,7 +4690,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>0.794933140277863</v>
+        <v>0.794933199882507</v>
       </c>
       <c r="H149" t="n">
         <v>123169</v>
@@ -4719,7 +4719,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G150" t="n">
-        <v>0.810478508472443</v>
+        <v>0.810478568077087</v>
       </c>
       <c r="H150" t="n">
         <v>18950</v>
@@ -4748,7 +4748,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G151" t="n">
-        <v>0.810478508472443</v>
+        <v>0.810478568077087</v>
       </c>
       <c r="H151" t="n">
         <v>11689</v>
@@ -4777,7 +4777,7 @@
         <v>1.17499995231628</v>
       </c>
       <c r="G152" t="n">
-        <v>0.830263614654541</v>
+        <v>0.830263435840607</v>
       </c>
       <c r="H152" t="n">
         <v>9829</v>
@@ -4806,7 +4806,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G153" t="n">
-        <v>0.828143894672394</v>
+        <v>0.828143775463104</v>
       </c>
       <c r="H153" t="n">
         <v>12703</v>
@@ -4835,7 +4835,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G154" t="n">
-        <v>0.828143894672394</v>
+        <v>0.828143775463104</v>
       </c>
       <c r="H154" t="n">
         <v>13805</v>
@@ -4864,7 +4864,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G155" t="n">
-        <v>0.819664359092712</v>
+        <v>0.819664478302002</v>
       </c>
       <c r="H155" t="n">
         <v>8786</v>
@@ -4922,7 +4922,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G157" t="n">
-        <v>0.812598466873169</v>
+        <v>0.812598288059235</v>
       </c>
       <c r="H157" t="n">
         <v>28352</v>
@@ -4980,7 +4980,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G159" t="n">
-        <v>0.823197424411774</v>
+        <v>0.823197543621063</v>
       </c>
       <c r="H159" t="n">
         <v>2845</v>
@@ -5009,7 +5009,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G160" t="n">
-        <v>0.814718186855316</v>
+        <v>0.814718246459961</v>
       </c>
       <c r="H160" t="n">
         <v>10823</v>
@@ -5038,7 +5038,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G161" t="n">
-        <v>0.828143894672394</v>
+        <v>0.828143775463104</v>
       </c>
       <c r="H161" t="n">
         <v>1989</v>
@@ -5067,7 +5067,7 @@
         <v>1.17200005054474</v>
       </c>
       <c r="G162" t="n">
-        <v>0.828143894672394</v>
+        <v>0.828143775463104</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G163" t="n">
-        <v>0.812598466873169</v>
+        <v>0.812598288059235</v>
       </c>
       <c r="H163" t="n">
         <v>4000</v>
@@ -5183,7 +5183,7 @@
         <v>1.125</v>
       </c>
       <c r="G166" t="n">
-        <v>0.794933259487152</v>
+        <v>0.794933199882507</v>
       </c>
       <c r="H166" t="n">
         <v>2100</v>
@@ -5212,7 +5212,7 @@
         <v>1.125</v>
       </c>
       <c r="G167" t="n">
-        <v>0.794933259487152</v>
+        <v>0.794933199882507</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>1.125</v>
       </c>
       <c r="G168" t="n">
-        <v>0.794933259487152</v>
+        <v>0.794933199882507</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>1.125</v>
       </c>
       <c r="G169" t="n">
-        <v>0.794933259487152</v>
+        <v>0.794933199882507</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>1.11699998378754</v>
       </c>
       <c r="G170" t="n">
-        <v>0.789280354976654</v>
+        <v>0.789280414581299</v>
       </c>
       <c r="H170" t="n">
         <v>6436</v>
@@ -5328,7 +5328,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G171" t="n">
-        <v>0.790693700313568</v>
+        <v>0.790693581104279</v>
       </c>
       <c r="H171" t="n">
         <v>3647</v>
@@ -5357,7 +5357,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G172" t="n">
-        <v>0.817544519901276</v>
+        <v>0.81754457950592</v>
       </c>
       <c r="H172" t="n">
         <v>1001</v>
@@ -5386,7 +5386,7 @@
         <v>1.15699994564056</v>
       </c>
       <c r="G173" t="n">
-        <v>0.817544519901276</v>
+        <v>0.81754457950592</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>1.13100004196167</v>
       </c>
       <c r="G174" t="n">
-        <v>0.799172818660736</v>
+        <v>0.799172878265381</v>
       </c>
       <c r="H174" t="n">
         <v>10205</v>
@@ -5444,7 +5444,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G175" t="n">
-        <v>0.804119110107422</v>
+        <v>0.804119169712067</v>
       </c>
       <c r="H175" t="n">
         <v>28896</v>
@@ -5473,7 +5473,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G176" t="n">
-        <v>0.803412437438965</v>
+        <v>0.80341249704361</v>
       </c>
       <c r="H176" t="n">
         <v>17140</v>
@@ -5502,7 +5502,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G177" t="n">
-        <v>0.805532336235046</v>
+        <v>0.805532395839691</v>
       </c>
       <c r="H177" t="n">
         <v>9813</v>
@@ -5531,7 +5531,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G178" t="n">
-        <v>0.805532336235046</v>
+        <v>0.805532395839691</v>
       </c>
       <c r="H178" t="n">
         <v>7350</v>
@@ -5560,7 +5560,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G179" t="n">
-        <v>0.795639932155609</v>
+        <v>0.795639872550964</v>
       </c>
       <c r="H179" t="n">
         <v>1000</v>
@@ -5589,7 +5589,7 @@
         <v>1.12300002574921</v>
       </c>
       <c r="G180" t="n">
-        <v>0.793520152568817</v>
+        <v>0.793520092964172</v>
       </c>
       <c r="H180" t="n">
         <v>3000</v>
@@ -5734,7 +5734,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G185" t="n">
-        <v>0.777268052101135</v>
+        <v>0.77726811170578</v>
       </c>
       <c r="H185" t="n">
         <v>5592</v>
@@ -5792,7 +5792,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G187" t="n">
-        <v>0.777268052101135</v>
+        <v>0.77726811170578</v>
       </c>
       <c r="H187" t="n">
         <v>888</v>
@@ -5908,7 +5908,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G191" t="n">
-        <v>0.763135850429535</v>
+        <v>0.76313591003418</v>
       </c>
       <c r="H191" t="n">
         <v>7200</v>
@@ -5937,7 +5937,7 @@
         <v>1.10199999809265</v>
       </c>
       <c r="G192" t="n">
-        <v>0.778681218624115</v>
+        <v>0.77868115901947</v>
       </c>
       <c r="H192" t="n">
         <v>28261</v>
@@ -5995,7 +5995,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G194" t="n">
-        <v>0.780094504356384</v>
+        <v>0.780094385147095</v>
       </c>
       <c r="H194" t="n">
         <v>2712</v>
@@ -6024,7 +6024,7 @@
         <v>1.10399997234344</v>
       </c>
       <c r="G195" t="n">
-        <v>0.780094504356384</v>
+        <v>0.780094385147095</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>1.11300003528595</v>
       </c>
       <c r="G196" t="n">
-        <v>0.786454021930695</v>
+        <v>0.786453902721405</v>
       </c>
       <c r="H196" t="n">
         <v>2822</v>
@@ -6111,7 +6111,7 @@
         <v>1.08899998664856</v>
       </c>
       <c r="G198" t="n">
-        <v>0.7694953083992</v>
+        <v>0.76949542760849</v>
       </c>
       <c r="H198" t="n">
         <v>6338</v>
@@ -6140,7 +6140,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G199" t="n">
-        <v>0.763135850429535</v>
+        <v>0.76313591003418</v>
       </c>
       <c r="H199" t="n">
         <v>8119</v>
@@ -6169,7 +6169,7 @@
         <v>1.08200001716614</v>
       </c>
       <c r="G200" t="n">
-        <v>0.764549195766449</v>
+        <v>0.764549136161804</v>
       </c>
       <c r="H200" t="n">
         <v>13900</v>
@@ -6198,7 +6198,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G201" t="n">
-        <v>0.766668975353241</v>
+        <v>0.766669034957886</v>
       </c>
       <c r="H201" t="n">
         <v>538</v>
@@ -6227,7 +6227,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G202" t="n">
-        <v>0.766668975353241</v>
+        <v>0.766669034957886</v>
       </c>
       <c r="H202" t="n">
         <v>950</v>
@@ -6256,7 +6256,7 @@
         <v>1.07299995422363</v>
       </c>
       <c r="G203" t="n">
-        <v>0.758189558982849</v>
+        <v>0.758189618587494</v>
       </c>
       <c r="H203" t="n">
         <v>37219</v>
@@ -6285,7 +6285,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G204" t="n">
-        <v>0.762429296970367</v>
+        <v>0.762429177761078</v>
       </c>
       <c r="H204" t="n">
         <v>11202</v>
@@ -6314,7 +6314,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G205" t="n">
-        <v>0.762429296970367</v>
+        <v>0.762429177761078</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>1.06700003147125</v>
       </c>
       <c r="G207" t="n">
-        <v>0.753949999809265</v>
+        <v>0.753950119018555</v>
       </c>
       <c r="H207" t="n">
         <v>1000</v>
@@ -6401,7 +6401,7 @@
         <v>1.06599998474121</v>
       </c>
       <c r="G208" t="n">
-        <v>0.753243327140808</v>
+        <v>0.753243386745453</v>
       </c>
       <c r="H208" t="n">
         <v>3800</v>
@@ -6430,7 +6430,7 @@
         <v>1.08800005912781</v>
       </c>
       <c r="G209" t="n">
-        <v>0.768788874149323</v>
+        <v>0.768788754940033</v>
       </c>
       <c r="H209" t="n">
         <v>24499</v>
@@ -6459,7 +6459,7 @@
         <v>1.0789999961853</v>
       </c>
       <c r="G210" t="n">
-        <v>0.762429296970367</v>
+        <v>0.762429177761078</v>
       </c>
       <c r="H210" t="n">
         <v>90686</v>
@@ -6488,7 +6488,7 @@
         <v>1.09700000286102</v>
       </c>
       <c r="G211" t="n">
-        <v>0.775148153305054</v>
+        <v>0.775148093700409</v>
       </c>
       <c r="H211" t="n">
         <v>3025</v>
@@ -6517,7 +6517,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G212" t="n">
-        <v>0.765962302684784</v>
+        <v>0.765962362289429</v>
       </c>
       <c r="H212" t="n">
         <v>9732</v>
@@ -6546,7 +6546,7 @@
         <v>1.07599997520447</v>
       </c>
       <c r="G213" t="n">
-        <v>0.760309517383575</v>
+        <v>0.760309457778931</v>
       </c>
       <c r="H213" t="n">
         <v>12828</v>
@@ -6575,7 +6575,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G214" t="n">
-        <v>0.756069779396057</v>
+        <v>0.756069839000702</v>
       </c>
       <c r="H214" t="n">
         <v>6518</v>
@@ -6604,7 +6604,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G215" t="n">
-        <v>0.749003708362579</v>
+        <v>0.749003767967224</v>
       </c>
       <c r="H215" t="n">
         <v>63131</v>
@@ -6662,7 +6662,7 @@
         <v>1.04700005054474</v>
       </c>
       <c r="G217" t="n">
-        <v>0.739817917346954</v>
+        <v>0.739817976951599</v>
       </c>
       <c r="H217" t="n">
         <v>13650</v>
@@ -6720,7 +6720,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G219" t="n">
-        <v>0.763135850429535</v>
+        <v>0.76313591003418</v>
       </c>
       <c r="H219" t="n">
         <v>7032</v>
@@ -6749,7 +6749,7 @@
         <v>1.06200003623962</v>
       </c>
       <c r="G220" t="n">
-        <v>0.750416934490204</v>
+        <v>0.750416994094849</v>
       </c>
       <c r="H220" t="n">
         <v>4011</v>
@@ -6778,7 +6778,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>0.734871685504913</v>
+        <v>0.734871625900269</v>
       </c>
       <c r="H221" t="n">
         <v>5600</v>
@@ -6865,7 +6865,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G224" t="n">
-        <v>0.763135850429535</v>
+        <v>0.76313591003418</v>
       </c>
       <c r="H224" t="n">
         <v>57951</v>
@@ -6894,7 +6894,7 @@
         <v>1.08700001239777</v>
       </c>
       <c r="G225" t="n">
-        <v>0.768082201480865</v>
+        <v>0.768082141876221</v>
       </c>
       <c r="H225" t="n">
         <v>10239</v>
@@ -6981,7 +6981,7 @@
         <v>1.04200005531311</v>
       </c>
       <c r="G228" t="n">
-        <v>0.736284911632538</v>
+        <v>0.736284852027893</v>
       </c>
       <c r="H228" t="n">
         <v>100619</v>
@@ -7010,7 +7010,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G229" t="n">
-        <v>0.734871685504913</v>
+        <v>0.734871625900269</v>
       </c>
       <c r="H229" t="n">
         <v>16036</v>
@@ -7039,7 +7039,7 @@
         <v>1.05599999427795</v>
       </c>
       <c r="G230" t="n">
-        <v>0.74617737531662</v>
+        <v>0.746177315711975</v>
       </c>
       <c r="H230" t="n">
         <v>14998</v>
@@ -7068,7 +7068,7 @@
         <v>1.03100001811981</v>
       </c>
       <c r="G231" t="n">
-        <v>0.728512108325958</v>
+        <v>0.728512167930603</v>
       </c>
       <c r="H231" t="n">
         <v>4443</v>
@@ -7097,7 +7097,7 @@
         <v>1.08399999141693</v>
       </c>
       <c r="G232" t="n">
-        <v>0.765962302684784</v>
+        <v>0.765962362289429</v>
       </c>
       <c r="H232" t="n">
         <v>215871</v>
@@ -7126,7 +7126,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G233" t="n">
-        <v>0.756069779396057</v>
+        <v>0.756069839000702</v>
       </c>
       <c r="H233" t="n">
         <v>105729</v>
@@ -7155,7 +7155,7 @@
         <v>1.04900002479553</v>
       </c>
       <c r="G234" t="n">
-        <v>0.741231083869934</v>
+        <v>0.741231143474579</v>
       </c>
       <c r="H234" t="n">
         <v>4100</v>
@@ -7213,7 +7213,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G236" t="n">
-        <v>0.763135850429535</v>
+        <v>0.76313591003418</v>
       </c>
       <c r="H236" t="n">
         <v>15273</v>
@@ -7242,7 +7242,7 @@
         <v>1.06099998950958</v>
       </c>
       <c r="G237" t="n">
-        <v>0.749710321426392</v>
+        <v>0.749710261821747</v>
       </c>
       <c r="H237" t="n">
         <v>25699</v>
@@ -7358,7 +7358,7 @@
         <v>1.05799996852875</v>
       </c>
       <c r="G241" t="n">
-        <v>0.747590482234955</v>
+        <v>0.747590601444244</v>
       </c>
       <c r="H241" t="n">
         <v>44596</v>
@@ -7445,7 +7445,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G244" t="n">
-        <v>0.763135850429535</v>
+        <v>0.76313591003418</v>
       </c>
       <c r="H244" t="n">
         <v>53989</v>
@@ -7474,7 +7474,7 @@
         <v>1.08500003814697</v>
       </c>
       <c r="G245" t="n">
-        <v>0.766668975353241</v>
+        <v>0.766669034957886</v>
       </c>
       <c r="H245" t="n">
         <v>33936</v>
@@ -7590,7 +7590,7 @@
         <v>1.13399994373322</v>
       </c>
       <c r="G249" t="n">
-        <v>0.801292598247528</v>
+        <v>0.801292657852173</v>
       </c>
       <c r="H249" t="n">
         <v>77039</v>
@@ -7619,7 +7619,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G250" t="n">
-        <v>0.807652056217194</v>
+        <v>0.807652235031128</v>
       </c>
       <c r="H250" t="n">
         <v>17089</v>
@@ -7648,7 +7648,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G251" t="n">
-        <v>0.810478508472443</v>
+        <v>0.810478568077087</v>
       </c>
       <c r="H251" t="n">
         <v>24050</v>
@@ -7677,7 +7677,7 @@
         <v>1.1360000371933</v>
       </c>
       <c r="G252" t="n">
-        <v>0.802705943584442</v>
+        <v>0.802706003189087</v>
       </c>
       <c r="H252" t="n">
         <v>78484</v>
@@ -7706,7 +7706,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G253" t="n">
-        <v>0.807652056217194</v>
+        <v>0.807652235031128</v>
       </c>
       <c r="H253" t="n">
         <v>18708</v>
@@ -7735,7 +7735,7 @@
         <v>1.14900004863739</v>
       </c>
       <c r="G254" t="n">
-        <v>0.811891734600067</v>
+        <v>0.811891853809357</v>
       </c>
       <c r="H254" t="n">
         <v>9835</v>
@@ -7764,7 +7764,7 @@
         <v>1.13800001144409</v>
       </c>
       <c r="G255" t="n">
-        <v>0.804119110107422</v>
+        <v>0.804119169712067</v>
       </c>
       <c r="H255" t="n">
         <v>12700</v>
@@ -7880,7 +7880,7 @@
         <v>1.17799997329712</v>
       </c>
       <c r="G259" t="n">
-        <v>0.832383334636688</v>
+        <v>0.832383453845978</v>
       </c>
       <c r="H259" t="n">
         <v>46937</v>
@@ -7909,7 +7909,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G260" t="n">
-        <v>0.821077704429626</v>
+        <v>0.821077764034271</v>
       </c>
       <c r="H260" t="n">
         <v>88087</v>
@@ -7938,7 +7938,7 @@
         <v>1.16700005531311</v>
       </c>
       <c r="G261" t="n">
-        <v>0.824610829353333</v>
+        <v>0.824610769748688</v>
       </c>
       <c r="H261" t="n">
         <v>85312</v>
@@ -7996,7 +7996,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G263" t="n">
-        <v>0.805532336235046</v>
+        <v>0.805532395839691</v>
       </c>
       <c r="H263" t="n">
         <v>51627</v>
@@ -8025,7 +8025,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G264" t="n">
-        <v>0.810478508472443</v>
+        <v>0.810478568077087</v>
       </c>
       <c r="H264" t="n">
         <v>15686</v>
@@ -8054,7 +8054,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G265" t="n">
-        <v>0.805532336235046</v>
+        <v>0.805532395839691</v>
       </c>
       <c r="H265" t="n">
         <v>78902</v>
@@ -8083,7 +8083,7 @@
         <v>1.11899995803833</v>
       </c>
       <c r="G266" t="n">
-        <v>0.790693700313568</v>
+        <v>0.790693581104279</v>
       </c>
       <c r="H266" t="n">
         <v>118800</v>
@@ -8112,7 +8112,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G267" t="n">
-        <v>0.814011573791504</v>
+        <v>0.814011454582214</v>
       </c>
       <c r="H267" t="n">
         <v>87083</v>
@@ -8170,7 +8170,7 @@
         <v>1.16199994087219</v>
       </c>
       <c r="G269" t="n">
-        <v>0.821077704429626</v>
+        <v>0.821077764034271</v>
       </c>
       <c r="H269" t="n">
         <v>153728</v>
@@ -8199,7 +8199,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G270" t="n">
-        <v>0.805532336235046</v>
+        <v>0.805532395839691</v>
       </c>
       <c r="H270" t="n">
         <v>96883</v>
@@ -8257,7 +8257,7 @@
         <v>1.14699995517731</v>
       </c>
       <c r="G272" t="n">
-        <v>0.810478508472443</v>
+        <v>0.810478568077087</v>
       </c>
       <c r="H272" t="n">
         <v>38619</v>
@@ -8286,7 +8286,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G273" t="n">
-        <v>0.823197424411774</v>
+        <v>0.823197543621063</v>
       </c>
       <c r="H273" t="n">
         <v>20752</v>
@@ -8344,7 +8344,7 @@
         <v>1.14300000667572</v>
       </c>
       <c r="G275" t="n">
-        <v>0.807652056217194</v>
+        <v>0.807652235031128</v>
       </c>
       <c r="H275" t="n">
         <v>27431</v>
@@ -8373,7 +8373,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G276" t="n">
-        <v>0.814011573791504</v>
+        <v>0.814011454582214</v>
       </c>
       <c r="H276" t="n">
         <v>114507</v>
@@ -8402,7 +8402,7 @@
         <v>1.15199995040894</v>
       </c>
       <c r="G277" t="n">
-        <v>0.814011573791504</v>
+        <v>0.814011454582214</v>
       </c>
       <c r="H277" t="n">
         <v>21412</v>
@@ -8431,7 +8431,7 @@
         <v>1.13999998569489</v>
       </c>
       <c r="G278" t="n">
-        <v>0.805532336235046</v>
+        <v>0.805532395839691</v>
       </c>
       <c r="H278" t="n">
         <v>12925</v>
@@ -8460,7 +8460,7 @@
         <v>1.12199997901917</v>
       </c>
       <c r="G279" t="n">
-        <v>0.792813420295715</v>
+        <v>0.792813360691071</v>
       </c>
       <c r="H279" t="n">
         <v>24416</v>
@@ -8489,7 +8489,7 @@
         <v>1.12600004673004</v>
       </c>
       <c r="G280" t="n">
-        <v>0.795639932155609</v>
+        <v>0.795639872550964</v>
       </c>
       <c r="H280" t="n">
         <v>9308</v>
@@ -8518,7 +8518,7 @@
         <v>1.13699996471405</v>
       </c>
       <c r="G281" t="n">
-        <v>0.803412437438965</v>
+        <v>0.80341249704361</v>
       </c>
       <c r="H281" t="n">
         <v>37977</v>
@@ -8663,7 +8663,7 @@
         <v>1.11500000953674</v>
       </c>
       <c r="G286" t="n">
-        <v>0.787867188453674</v>
+        <v>0.787867069244385</v>
       </c>
       <c r="H286" t="n">
         <v>36905</v>
@@ -8721,7 +8721,7 @@
         <v>1.15900003910065</v>
       </c>
       <c r="G288" t="n">
-        <v>0.818957924842834</v>
+        <v>0.818957805633545</v>
       </c>
       <c r="H288" t="n">
         <v>47950</v>
@@ -8750,7 +8750,7 @@
         <v>1.15100002288818</v>
       </c>
       <c r="G289" t="n">
-        <v>0.813304960727692</v>
+        <v>0.813305079936981</v>
       </c>
       <c r="H289" t="n">
         <v>46721</v>
@@ -8779,7 +8779,7 @@
         <v>1.1690000295639</v>
       </c>
       <c r="G290" t="n">
-        <v>0.826023876667023</v>
+        <v>0.826024055480957</v>
       </c>
       <c r="H290" t="n">
         <v>42750</v>
@@ -8808,7 +8808,7 @@
         <v>1.18599998950958</v>
       </c>
       <c r="G291" t="n">
-        <v>0.838036239147186</v>
+        <v>0.838036179542542</v>
       </c>
       <c r="H291" t="n">
         <v>68181</v>
@@ -8837,7 +8837,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G292" t="n">
-        <v>0.823197424411774</v>
+        <v>0.823197543621063</v>
       </c>
       <c r="H292" t="n">
         <v>34254</v>
@@ -8866,7 +8866,7 @@
         <v>1.16499996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>0.823197424411774</v>
+        <v>0.823197543621063</v>
       </c>
       <c r="H293" t="n">
         <v>27441</v>
@@ -8895,7 +8895,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G294" t="n">
-        <v>0.819664359092712</v>
+        <v>0.819664478302002</v>
       </c>
       <c r="H294" t="n">
         <v>25318</v>
@@ -8924,7 +8924,7 @@
         <v>1.15299999713898</v>
       </c>
       <c r="G295" t="n">
-        <v>0.814718186855316</v>
+        <v>0.814718246459961</v>
       </c>
       <c r="H295" t="n">
         <v>34418</v>
@@ -9040,7 +9040,7 @@
         <v>1.17700004577637</v>
       </c>
       <c r="G299" t="n">
-        <v>0.831676959991455</v>
+        <v>0.831676781177521</v>
       </c>
       <c r="H299" t="n">
         <v>52276</v>
@@ -9069,7 +9069,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G300" t="n">
-        <v>0.875486433506012</v>
+        <v>0.875486373901367</v>
       </c>
       <c r="H300" t="n">
         <v>326295</v>
@@ -9098,7 +9098,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G301" t="n">
-        <v>0.879019439220428</v>
+        <v>0.879019498825073</v>
       </c>
       <c r="H301" t="n">
         <v>192725</v>
@@ -9127,7 +9127,7 @@
         <v>1.23099994659424</v>
       </c>
       <c r="G302" t="n">
-        <v>0.869833767414093</v>
+        <v>0.869833588600159</v>
       </c>
       <c r="H302" t="n">
         <v>86772</v>
@@ -9185,7 +9185,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G304" t="n">
-        <v>0.88255250453949</v>
+        <v>0.882552623748779</v>
       </c>
       <c r="H304" t="n">
         <v>53635</v>
@@ -9214,7 +9214,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G305" t="n">
-        <v>0.886792063713074</v>
+        <v>0.886792182922363</v>
       </c>
       <c r="H305" t="n">
         <v>33570</v>
@@ -9243,7 +9243,7 @@
         <v>1.23399996757507</v>
       </c>
       <c r="G306" t="n">
-        <v>0.871953547000885</v>
+        <v>0.871953368186951</v>
       </c>
       <c r="H306" t="n">
         <v>38799</v>
@@ -9272,7 +9272,7 @@
         <v>1.22800004482269</v>
       </c>
       <c r="G307" t="n">
-        <v>0.867713868618011</v>
+        <v>0.867713749408722</v>
       </c>
       <c r="H307" t="n">
         <v>43446</v>
@@ -9301,7 +9301,7 @@
         <v>1.2389999628067</v>
       </c>
       <c r="G308" t="n">
-        <v>0.875486433506012</v>
+        <v>0.875486373901367</v>
       </c>
       <c r="H308" t="n">
         <v>35901</v>
@@ -9388,7 +9388,7 @@
         <v>1.24899995326996</v>
       </c>
       <c r="G311" t="n">
-        <v>0.88255250453949</v>
+        <v>0.882552623748779</v>
       </c>
       <c r="H311" t="n">
         <v>55144</v>
@@ -9417,7 +9417,7 @@
         <v>1.24399995803833</v>
       </c>
       <c r="G312" t="n">
-        <v>0.879019439220428</v>
+        <v>0.879019498825073</v>
       </c>
       <c r="H312" t="n">
         <v>47950</v>
@@ -9446,7 +9446,7 @@
         <v>1.33599996566772</v>
       </c>
       <c r="G313" t="n">
-        <v>0.944027423858643</v>
+        <v>0.944027245044708</v>
       </c>
       <c r="H313" t="n">
         <v>332929</v>
@@ -9475,7 +9475,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G314" t="n">
-        <v>0.932721734046936</v>
+        <v>0.932721674442291</v>
       </c>
       <c r="H314" t="n">
         <v>297740</v>
@@ -9504,7 +9504,7 @@
         <v>1.32000005245209</v>
       </c>
       <c r="G315" t="n">
-        <v>0.932721734046936</v>
+        <v>0.932721674442291</v>
       </c>
       <c r="H315" t="n">
         <v>96276</v>
@@ -9533,7 +9533,7 @@
         <v>1.39800000190735</v>
       </c>
       <c r="G316" t="n">
-        <v>0.987837076187134</v>
+        <v>0.987837255001068</v>
       </c>
       <c r="H316" t="n">
         <v>265572</v>
@@ -9562,7 +9562,7 @@
         <v>1.44099998474121</v>
       </c>
       <c r="G317" t="n">
-        <v>1.01822113990784</v>
+        <v>1.01822125911713</v>
       </c>
       <c r="H317" t="n">
         <v>356786</v>
@@ -9591,7 +9591,7 @@
         <v>1.44799995422363</v>
       </c>
       <c r="G318" t="n">
-        <v>1.02316737174988</v>
+        <v>1.02316749095917</v>
       </c>
       <c r="H318" t="n">
         <v>91069</v>
@@ -9678,7 +9678,7 @@
         <v>1.4190000295639</v>
       </c>
       <c r="G321" t="n">
-        <v>1.00267577171326</v>
+        <v>1.00267589092255</v>
       </c>
       <c r="H321" t="n">
         <v>43587</v>
@@ -9736,7 +9736,7 @@
         <v>1.39100003242493</v>
       </c>
       <c r="G323" t="n">
-        <v>0.982890725135803</v>
+        <v>0.982890784740448</v>
       </c>
       <c r="H323" t="n">
         <v>38798</v>
@@ -9765,7 +9765,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G324" t="n">
-        <v>0.975118041038513</v>
+        <v>0.975118160247803</v>
       </c>
       <c r="H324" t="n">
         <v>65133</v>
@@ -9823,7 +9823,7 @@
         <v>1.36699998378754</v>
       </c>
       <c r="G326" t="n">
-        <v>0.965932309627533</v>
+        <v>0.965932071208954</v>
       </c>
       <c r="H326" t="n">
         <v>63700</v>
@@ -9852,7 +9852,7 @@
         <v>1.35000002384186</v>
       </c>
       <c r="G327" t="n">
-        <v>0.953919768333435</v>
+        <v>0.953920006752014</v>
       </c>
       <c r="H327" t="n">
         <v>28423</v>
@@ -9881,7 +9881,7 @@
         <v>1.37800002098083</v>
       </c>
       <c r="G328" t="n">
-        <v>0.973704874515533</v>
+        <v>0.973704934120178</v>
       </c>
       <c r="H328" t="n">
         <v>67239</v>
@@ -9910,7 +9910,7 @@
         <v>1.38800001144409</v>
       </c>
       <c r="G329" t="n">
-        <v>0.980770826339722</v>
+        <v>0.980771064758301</v>
       </c>
       <c r="H329" t="n">
         <v>150045</v>
@@ -9939,7 +9939,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G330" t="n">
-        <v>1.00832867622375</v>
+        <v>1.00832855701447</v>
       </c>
       <c r="H330" t="n">
         <v>68475</v>
@@ -9968,7 +9968,7 @@
         <v>1.43900001049042</v>
       </c>
       <c r="G331" t="n">
-        <v>1.0168080329895</v>
+        <v>1.01680791378021</v>
       </c>
       <c r="H331" t="n">
         <v>138888</v>
@@ -9997,7 +9997,7 @@
         <v>1.40900003910065</v>
       </c>
       <c r="G332" t="n">
-        <v>0.995609700679779</v>
+        <v>0.995609760284424</v>
       </c>
       <c r="H332" t="n">
         <v>56328</v>
@@ -10026,7 +10026,7 @@
         <v>1.42700004577637</v>
       </c>
       <c r="G333" t="n">
-        <v>1.00832867622375</v>
+        <v>1.00832855701447</v>
       </c>
       <c r="H333" t="n">
         <v>64955</v>
@@ -10113,7 +10113,7 @@
         <v>1.49800002574921</v>
       </c>
       <c r="G336" t="n">
-        <v>1.05849766731262</v>
+        <v>1.05849778652191</v>
       </c>
       <c r="H336" t="n">
         <v>110437</v>
@@ -10142,7 +10142,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G337" t="n">
-        <v>1.06556391716003</v>
+        <v>1.06556379795074</v>
       </c>
       <c r="H337" t="n">
         <v>35387</v>
@@ -10200,7 +10200,7 @@
         <v>1.52100002765656</v>
       </c>
       <c r="G339" t="n">
-        <v>1.07474982738495</v>
+        <v>1.07474970817566</v>
       </c>
       <c r="H339" t="n">
         <v>113847</v>
@@ -10258,7 +10258,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G341" t="n">
-        <v>1.13057172298431</v>
+        <v>1.1305718421936</v>
       </c>
       <c r="H341" t="n">
         <v>279183</v>
@@ -10287,7 +10287,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G342" t="n">
-        <v>1.15671598911285</v>
+        <v>1.15671622753143</v>
       </c>
       <c r="H342" t="n">
         <v>228181</v>
@@ -10316,7 +10316,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G343" t="n">
-        <v>1.17226147651672</v>
+        <v>1.17226159572601</v>
       </c>
       <c r="H343" t="n">
         <v>239666</v>
@@ -10461,7 +10461,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G348" t="n">
-        <v>1.17296826839447</v>
+        <v>1.17296814918518</v>
       </c>
       <c r="H348" t="n">
         <v>73930</v>
@@ -10548,7 +10548,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G351" t="n">
-        <v>1.16590225696564</v>
+        <v>1.16590201854706</v>
       </c>
       <c r="H351" t="n">
         <v>70853</v>
@@ -10606,7 +10606,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G353" t="n">
-        <v>1.1553031206131</v>
+        <v>1.15530300140381</v>
       </c>
       <c r="H353" t="n">
         <v>93517</v>
@@ -10635,7 +10635,7 @@
         <v>1.61800003051758</v>
       </c>
       <c r="G354" t="n">
-        <v>1.14329051971436</v>
+        <v>1.14329040050507</v>
       </c>
       <c r="H354" t="n">
         <v>15063</v>
@@ -10664,7 +10664,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G355" t="n">
-        <v>1.16590225696564</v>
+        <v>1.16590201854706</v>
       </c>
       <c r="H355" t="n">
         <v>33140</v>
@@ -10693,7 +10693,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G356" t="n">
-        <v>1.16590225696564</v>
+        <v>1.16590201854706</v>
       </c>
       <c r="H356" t="n">
         <v>63962</v>
@@ -10780,7 +10780,7 @@
         <v>1.70799994468689</v>
       </c>
       <c r="G359" t="n">
-        <v>1.2068852186203</v>
+        <v>1.20688533782959</v>
       </c>
       <c r="H359" t="n">
         <v>119952</v>
@@ -10809,7 +10809,7 @@
         <v>1.68299996852875</v>
       </c>
       <c r="G360" t="n">
-        <v>1.18921995162964</v>
+        <v>1.18922007083893</v>
       </c>
       <c r="H360" t="n">
         <v>31825</v>
@@ -10925,7 +10925,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G364" t="n">
-        <v>1.20829856395721</v>
+        <v>1.2082986831665</v>
       </c>
       <c r="H364" t="n">
         <v>33548</v>
@@ -10954,7 +10954,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>1.20829856395721</v>
+        <v>1.2082986831665</v>
       </c>
       <c r="H365" t="n">
         <v>53843</v>
@@ -11041,7 +11041,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G368" t="n">
-        <v>1.24362897872925</v>
+        <v>1.24362874031067</v>
       </c>
       <c r="H368" t="n">
         <v>131416</v>
@@ -11157,7 +11157,7 @@
         <v>1.62100005149841</v>
       </c>
       <c r="G372" t="n">
-        <v>1.14541041851044</v>
+        <v>1.14541053771973</v>
       </c>
       <c r="H372" t="n">
         <v>73103</v>
@@ -11244,7 +11244,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G375" t="n">
-        <v>1.10937333106995</v>
+        <v>1.10937356948853</v>
       </c>
       <c r="H375" t="n">
         <v>31784</v>
@@ -11273,7 +11273,7 @@
         <v>1.57700002193451</v>
       </c>
       <c r="G376" t="n">
-        <v>1.11431980133057</v>
+        <v>1.11431992053986</v>
       </c>
       <c r="H376" t="n">
         <v>10123</v>
@@ -11302,7 +11302,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G377" t="n">
-        <v>1.12067914009094</v>
+        <v>1.12067925930023</v>
       </c>
       <c r="H377" t="n">
         <v>7831</v>
@@ -11476,7 +11476,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>1.09524130821228</v>
+        <v>1.09524142742157</v>
       </c>
       <c r="H383" t="n">
         <v>29761</v>
@@ -11505,7 +11505,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G384" t="n">
-        <v>1.09806764125824</v>
+        <v>1.09806787967682</v>
       </c>
       <c r="H384" t="n">
         <v>16369</v>
@@ -11534,7 +11534,7 @@
         <v>1.51999998092651</v>
       </c>
       <c r="G385" t="n">
-        <v>1.0740430355072</v>
+        <v>1.07404315471649</v>
       </c>
       <c r="H385" t="n">
         <v>42277</v>
@@ -11563,7 +11563,7 @@
         <v>1.54100000858307</v>
       </c>
       <c r="G386" t="n">
-        <v>1.0888819694519</v>
+        <v>1.08888208866119</v>
       </c>
       <c r="H386" t="n">
         <v>17156</v>
@@ -11592,7 +11592,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G387" t="n">
-        <v>1.10937333106995</v>
+        <v>1.10937356948853</v>
       </c>
       <c r="H387" t="n">
         <v>10178</v>
@@ -11621,7 +11621,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G388" t="n">
-        <v>1.10937333106995</v>
+        <v>1.10937356948853</v>
       </c>
       <c r="H388" t="n">
         <v>20357</v>
@@ -11650,7 +11650,7 @@
         <v>1.60199999809265</v>
       </c>
       <c r="G389" t="n">
-        <v>1.13198494911194</v>
+        <v>1.13198482990265</v>
       </c>
       <c r="H389" t="n">
         <v>35582</v>
@@ -11679,7 +11679,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G390" t="n">
-        <v>1.13057172298431</v>
+        <v>1.1305718421936</v>
       </c>
       <c r="H390" t="n">
         <v>9171</v>
@@ -11737,7 +11737,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G392" t="n">
-        <v>1.22243070602417</v>
+        <v>1.22243082523346</v>
       </c>
       <c r="H392" t="n">
         <v>252211</v>
@@ -11795,7 +11795,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G394" t="n">
-        <v>1.24998831748962</v>
+        <v>1.24998843669891</v>
       </c>
       <c r="H394" t="n">
         <v>109660</v>
@@ -11824,7 +11824,7 @@
         <v>1.81900000572205</v>
       </c>
       <c r="G395" t="n">
-        <v>1.28531861305237</v>
+        <v>1.28531873226166</v>
       </c>
       <c r="H395" t="n">
         <v>232089</v>
@@ -11853,7 +11853,7 @@
         <v>1.78900003433228</v>
       </c>
       <c r="G396" t="n">
-        <v>1.26412045955658</v>
+        <v>1.26412057876587</v>
       </c>
       <c r="H396" t="n">
         <v>129871</v>
@@ -11882,7 +11882,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G397" t="n">
-        <v>1.29309153556824</v>
+        <v>1.29309141635895</v>
       </c>
       <c r="H397" t="n">
         <v>153116</v>
@@ -11911,7 +11911,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G398" t="n">
-        <v>1.27895903587341</v>
+        <v>1.2789591550827</v>
       </c>
       <c r="H398" t="n">
         <v>109977</v>
@@ -12027,7 +12027,7 @@
         <v>1.75</v>
       </c>
       <c r="G402" t="n">
-        <v>1.26473045349121</v>
+        <v>1.2647305727005</v>
       </c>
       <c r="H402" t="n">
         <v>29596</v>
@@ -12114,7 +12114,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G405" t="n">
-        <v>1.29002499580383</v>
+        <v>1.29002511501312</v>
       </c>
       <c r="H405" t="n">
         <v>46814</v>
@@ -12172,7 +12172,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G407" t="n">
-        <v>1.30086553096771</v>
+        <v>1.300865650177</v>
       </c>
       <c r="H407" t="n">
         <v>46354</v>
@@ -12201,7 +12201,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G408" t="n">
-        <v>1.30809247493744</v>
+        <v>1.30809259414673</v>
       </c>
       <c r="H408" t="n">
         <v>53238</v>
@@ -12230,7 +12230,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G409" t="n">
-        <v>1.30809247493744</v>
+        <v>1.30809259414673</v>
       </c>
       <c r="H409" t="n">
         <v>65937</v>
@@ -12259,7 +12259,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G410" t="n">
-        <v>1.32399213314056</v>
+        <v>1.32399225234985</v>
       </c>
       <c r="H410" t="n">
         <v>69723</v>
@@ -12288,7 +12288,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G411" t="n">
-        <v>1.32977390289307</v>
+        <v>1.32977366447449</v>
       </c>
       <c r="H411" t="n">
         <v>23299</v>
@@ -12375,7 +12375,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G414" t="n">
-        <v>1.30086553096771</v>
+        <v>1.300865650177</v>
       </c>
       <c r="H414" t="n">
         <v>41380</v>
@@ -12404,7 +12404,7 @@
         <v>1.80099999904633</v>
       </c>
       <c r="G415" t="n">
-        <v>1.30158841609955</v>
+        <v>1.30158829689026</v>
       </c>
       <c r="H415" t="n">
         <v>8025</v>
@@ -12433,7 +12433,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G416" t="n">
-        <v>1.32471477985382</v>
+        <v>1.32471489906311</v>
       </c>
       <c r="H416" t="n">
         <v>41383</v>
@@ -12462,7 +12462,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G417" t="n">
-        <v>1.32543754577637</v>
+        <v>1.32543778419495</v>
       </c>
       <c r="H417" t="n">
         <v>12218</v>
@@ -12491,7 +12491,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G418" t="n">
-        <v>1.31893312931061</v>
+        <v>1.31893336772919</v>
       </c>
       <c r="H418" t="n">
         <v>11911</v>
@@ -12520,7 +12520,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G419" t="n">
-        <v>1.30664730072021</v>
+        <v>1.30664718151093</v>
       </c>
       <c r="H419" t="n">
         <v>4813</v>
@@ -12549,7 +12549,7 @@
         <v>1.82700002193451</v>
       </c>
       <c r="G420" t="n">
-        <v>1.3203786611557</v>
+        <v>1.32037878036499</v>
       </c>
       <c r="H420" t="n">
         <v>8368</v>
@@ -12578,7 +12578,7 @@
         <v>1.83299994468689</v>
       </c>
       <c r="G421" t="n">
-        <v>1.32471477985382</v>
+        <v>1.32471489906311</v>
       </c>
       <c r="H421" t="n">
         <v>8608</v>
@@ -12694,7 +12694,7 @@
         <v>1.75</v>
       </c>
       <c r="G425" t="n">
-        <v>1.26473045349121</v>
+        <v>1.2647305727005</v>
       </c>
       <c r="H425" t="n">
         <v>24346</v>
@@ -12752,7 +12752,7 @@
         <v>1.76300001144409</v>
       </c>
       <c r="G427" t="n">
-        <v>1.27412557601929</v>
+        <v>1.27412569522858</v>
       </c>
       <c r="H427" t="n">
         <v>20649</v>
@@ -12781,7 +12781,7 @@
         <v>1.76900005340576</v>
       </c>
       <c r="G428" t="n">
-        <v>1.2784618139267</v>
+        <v>1.27846193313599</v>
       </c>
       <c r="H428" t="n">
         <v>10139</v>
@@ -12810,7 +12810,7 @@
         <v>1.75</v>
       </c>
       <c r="G429" t="n">
-        <v>1.26473045349121</v>
+        <v>1.2647305727005</v>
       </c>
       <c r="H429" t="n">
         <v>31026</v>
@@ -12839,7 +12839,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G430" t="n">
-        <v>1.25533533096313</v>
+        <v>1.25533545017242</v>
       </c>
       <c r="H430" t="n">
         <v>25070</v>
@@ -12868,7 +12868,7 @@
         <v>1.7039999961853</v>
       </c>
       <c r="G431" t="n">
-        <v>1.23148620128632</v>
+        <v>1.23148596286774</v>
       </c>
       <c r="H431" t="n">
         <v>32868</v>
@@ -12955,7 +12955,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>1.25750350952148</v>
+        <v>1.25750339031219</v>
       </c>
       <c r="H434" t="n">
         <v>46583</v>
@@ -13013,7 +13013,7 @@
         <v>1.80400002002716</v>
       </c>
       <c r="G436" t="n">
-        <v>1.30375647544861</v>
+        <v>1.30375635623932</v>
       </c>
       <c r="H436" t="n">
         <v>82389</v>
@@ -13071,7 +13071,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G438" t="n">
-        <v>1.30086553096771</v>
+        <v>1.300865650177</v>
       </c>
       <c r="H438" t="n">
         <v>30599</v>
@@ -13100,7 +13100,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G439" t="n">
-        <v>1.32832849025726</v>
+        <v>1.32832837104797</v>
       </c>
       <c r="H439" t="n">
         <v>61214</v>
@@ -13129,7 +13129,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G440" t="n">
-        <v>1.30953812599182</v>
+        <v>1.30953824520111</v>
       </c>
       <c r="H440" t="n">
         <v>58757</v>
@@ -13158,7 +13158,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G441" t="n">
-        <v>1.32977390289307</v>
+        <v>1.32977366447449</v>
       </c>
       <c r="H441" t="n">
         <v>71713</v>
@@ -13187,7 +13187,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G442" t="n">
-        <v>1.33411002159119</v>
+        <v>1.3341099023819</v>
       </c>
       <c r="H442" t="n">
         <v>73503</v>
@@ -13245,7 +13245,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G444" t="n">
-        <v>1.32832849025726</v>
+        <v>1.32832837104797</v>
       </c>
       <c r="H444" t="n">
         <v>31379</v>
@@ -13274,7 +13274,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G445" t="n">
-        <v>1.31748783588409</v>
+        <v>1.3174877166748</v>
       </c>
       <c r="H445" t="n">
         <v>22308</v>
@@ -13361,7 +13361,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G448" t="n">
-        <v>1.31676518917084</v>
+        <v>1.31676495075226</v>
       </c>
       <c r="H448" t="n">
         <v>28797</v>
@@ -13419,7 +13419,7 @@
         <v>1.81200003623962</v>
       </c>
       <c r="G450" t="n">
-        <v>1.30953812599182</v>
+        <v>1.30953824520111</v>
       </c>
       <c r="H450" t="n">
         <v>54623</v>
@@ -13448,7 +13448,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G451" t="n">
-        <v>1.32977390289307</v>
+        <v>1.32977366447449</v>
       </c>
       <c r="H451" t="n">
         <v>84075</v>
@@ -13477,7 +13477,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G452" t="n">
-        <v>1.31821060180664</v>
+        <v>1.31821048259735</v>
       </c>
       <c r="H452" t="n">
         <v>55729</v>
@@ -13535,7 +13535,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G454" t="n">
-        <v>1.30086553096771</v>
+        <v>1.300865650177</v>
       </c>
       <c r="H454" t="n">
         <v>79893</v>
@@ -13651,7 +13651,7 @@
         <v>1.91299998760223</v>
       </c>
       <c r="G458" t="n">
-        <v>1.38253104686737</v>
+        <v>1.38253116607666</v>
       </c>
       <c r="H458" t="n">
         <v>278421</v>
@@ -13709,7 +13709,7 @@
         <v>1.94599997997284</v>
       </c>
       <c r="G460" t="n">
-        <v>1.40638029575348</v>
+        <v>1.4063800573349</v>
       </c>
       <c r="H460" t="n">
         <v>109912</v>
@@ -13738,7 +13738,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G461" t="n">
-        <v>1.48154151439667</v>
+        <v>1.48154127597809</v>
       </c>
       <c r="H461" t="n">
         <v>226047</v>
@@ -13796,7 +13796,7 @@
         <v>2.03600001335144</v>
       </c>
       <c r="G463" t="n">
-        <v>1.47142362594604</v>
+        <v>1.47142374515533</v>
       </c>
       <c r="H463" t="n">
         <v>121640</v>
@@ -13825,7 +13825,7 @@
         <v>1.99399995803833</v>
       </c>
       <c r="G464" t="n">
-        <v>1.44106996059418</v>
+        <v>1.44107007980347</v>
       </c>
       <c r="H464" t="n">
         <v>71357</v>
@@ -13854,7 +13854,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G465" t="n">
-        <v>1.45263338088989</v>
+        <v>1.45263314247131</v>
       </c>
       <c r="H465" t="n">
         <v>311150</v>
@@ -13912,7 +13912,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G467" t="n">
-        <v>1.45552408695221</v>
+        <v>1.4555242061615</v>
       </c>
       <c r="H467" t="n">
         <v>48355</v>
@@ -13970,7 +13970,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G469" t="n">
-        <v>1.45696938037872</v>
+        <v>1.45696949958801</v>
       </c>
       <c r="H469" t="n">
         <v>55943</v>
@@ -13999,7 +13999,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>1.45986032485962</v>
+        <v>1.45986044406891</v>
       </c>
       <c r="H470" t="n">
         <v>90612</v>
@@ -14028,7 +14028,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>1.45986032485962</v>
+        <v>1.45986044406891</v>
       </c>
       <c r="H471" t="n">
         <v>31899</v>
@@ -14057,7 +14057,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G472" t="n">
-        <v>1.45986032485962</v>
+        <v>1.45986044406891</v>
       </c>
       <c r="H472" t="n">
         <v>59305</v>
@@ -14144,7 +14144,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G475" t="n">
-        <v>1.40782582759857</v>
+        <v>1.40782558917999</v>
       </c>
       <c r="H475" t="n">
         <v>50922</v>
@@ -14173,7 +14173,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G476" t="n">
-        <v>1.36590886116028</v>
+        <v>1.36590898036957</v>
       </c>
       <c r="H476" t="n">
         <v>100585</v>
@@ -14202,7 +14202,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G477" t="n">
-        <v>1.32977390289307</v>
+        <v>1.32977366447449</v>
       </c>
       <c r="H477" t="n">
         <v>124958</v>
@@ -14231,7 +14231,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G478" t="n">
-        <v>1.33844614028931</v>
+        <v>1.3384462594986</v>
       </c>
       <c r="H478" t="n">
         <v>28293</v>
@@ -14260,7 +14260,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G479" t="n">
-        <v>1.32110118865967</v>
+        <v>1.32110130786896</v>
       </c>
       <c r="H479" t="n">
         <v>49724</v>
@@ -14289,7 +14289,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G480" t="n">
-        <v>1.27195763587952</v>
+        <v>1.27195739746094</v>
       </c>
       <c r="H480" t="n">
         <v>70217</v>
@@ -14318,7 +14318,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G481" t="n">
-        <v>1.22859537601471</v>
+        <v>1.22859525680542</v>
       </c>
       <c r="H481" t="n">
         <v>275249</v>
@@ -14405,7 +14405,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G484" t="n">
-        <v>1.30086553096771</v>
+        <v>1.300865650177</v>
       </c>
       <c r="H484" t="n">
         <v>91456</v>
@@ -14521,7 +14521,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G488" t="n">
-        <v>1.41649830341339</v>
+        <v>1.4164981842041</v>
       </c>
       <c r="H488" t="n">
         <v>64388</v>
@@ -14550,7 +14550,7 @@
         <v>1.95899999141693</v>
       </c>
       <c r="G489" t="n">
-        <v>1.41577553749084</v>
+        <v>1.41577529907227</v>
       </c>
       <c r="H489" t="n">
         <v>34628</v>
@@ -14637,7 +14637,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G492" t="n">
-        <v>1.34928679466248</v>
+        <v>1.3492865562439</v>
       </c>
       <c r="H492" t="n">
         <v>22453</v>
@@ -14666,7 +14666,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G493" t="n">
-        <v>1.3370007276535</v>
+        <v>1.33700084686279</v>
       </c>
       <c r="H493" t="n">
         <v>38990</v>
@@ -14695,7 +14695,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G494" t="n">
-        <v>1.3370007276535</v>
+        <v>1.33700084686279</v>
       </c>
       <c r="H494" t="n">
         <v>15722</v>
@@ -14724,7 +14724,7 @@
         <v>1.86699998378754</v>
       </c>
       <c r="G495" t="n">
-        <v>1.34928679466248</v>
+        <v>1.3492865562439</v>
       </c>
       <c r="H495" t="n">
         <v>13411</v>
@@ -14753,7 +14753,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G496" t="n">
-        <v>1.3261604309082</v>
+        <v>1.32616031169891</v>
       </c>
       <c r="H496" t="n">
         <v>20610</v>
@@ -14811,7 +14811,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G498" t="n">
-        <v>1.33627808094025</v>
+        <v>1.33627796173096</v>
       </c>
       <c r="H498" t="n">
         <v>8446</v>
@@ -14869,7 +14869,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G500" t="n">
-        <v>1.3261604309082</v>
+        <v>1.32616031169891</v>
       </c>
       <c r="H500" t="n">
         <v>27772</v>
@@ -14898,7 +14898,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G501" t="n">
-        <v>1.30592453479767</v>
+        <v>1.30592465400696</v>
       </c>
       <c r="H501" t="n">
         <v>12993</v>
@@ -14927,7 +14927,7 @@
         <v>1.82299995422363</v>
       </c>
       <c r="G502" t="n">
-        <v>1.31748783588409</v>
+        <v>1.3174877166748</v>
       </c>
       <c r="H502" t="n">
         <v>15950</v>
@@ -14956,7 +14956,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G503" t="n">
-        <v>1.30592453479767</v>
+        <v>1.30592465400696</v>
       </c>
       <c r="H503" t="n">
         <v>12383</v>
@@ -14985,7 +14985,7 @@
         <v>1.80799996852875</v>
       </c>
       <c r="G504" t="n">
-        <v>1.30664730072021</v>
+        <v>1.30664718151093</v>
       </c>
       <c r="H504" t="n">
         <v>11897</v>
@@ -15014,7 +15014,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G505" t="n">
-        <v>1.29725217819214</v>
+        <v>1.29725205898285</v>
       </c>
       <c r="H505" t="n">
         <v>22911</v>
@@ -15043,7 +15043,7 @@
         <v>1.79700005054474</v>
       </c>
       <c r="G506" t="n">
-        <v>1.29869759082794</v>
+        <v>1.29869747161865</v>
       </c>
       <c r="H506" t="n">
         <v>15052</v>
@@ -15159,7 +15159,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G510" t="n">
-        <v>1.32110118865967</v>
+        <v>1.32110130786896</v>
       </c>
       <c r="H510" t="n">
         <v>5942</v>
@@ -15188,7 +15188,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G511" t="n">
-        <v>1.30520176887512</v>
+        <v>1.30520164966583</v>
       </c>
       <c r="H511" t="n">
         <v>16771</v>
@@ -15217,7 +15217,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G512" t="n">
-        <v>1.3370007276535</v>
+        <v>1.33700084686279</v>
       </c>
       <c r="H512" t="n">
         <v>12936</v>
@@ -15362,7 +15362,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G517" t="n">
-        <v>1.42733883857727</v>
+        <v>1.42733871936798</v>
       </c>
       <c r="H517" t="n">
         <v>186014</v>
@@ -15391,7 +15391,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G518" t="n">
-        <v>1.41649830341339</v>
+        <v>1.4164981842041</v>
       </c>
       <c r="H518" t="n">
         <v>102239</v>
@@ -15565,7 +15565,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>1.41649830341339</v>
+        <v>1.4164981842041</v>
       </c>
       <c r="H524" t="n">
         <v>38446</v>
@@ -15623,7 +15623,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G526" t="n">
-        <v>1.42733883857727</v>
+        <v>1.42733871936798</v>
       </c>
       <c r="H526" t="n">
         <v>43464</v>
@@ -15826,7 +15826,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G533" t="n">
-        <v>1.38759005069733</v>
+        <v>1.38758993148804</v>
       </c>
       <c r="H533" t="n">
         <v>21681</v>
@@ -15855,7 +15855,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G534" t="n">
-        <v>1.38759005069733</v>
+        <v>1.38758993148804</v>
       </c>
       <c r="H534" t="n">
         <v>30821</v>
@@ -15884,7 +15884,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G535" t="n">
-        <v>1.36952221393585</v>
+        <v>1.36952245235443</v>
       </c>
       <c r="H535" t="n">
         <v>22450</v>
@@ -15913,7 +15913,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G536" t="n">
-        <v>1.31170630455017</v>
+        <v>1.31170606613159</v>
       </c>
       <c r="H536" t="n">
         <v>99486</v>
@@ -15942,7 +15942,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G537" t="n">
-        <v>1.25750350952148</v>
+        <v>1.25750339031219</v>
       </c>
       <c r="H537" t="n">
         <v>111081</v>
@@ -16000,7 +16000,7 @@
         <v>1.75</v>
       </c>
       <c r="G539" t="n">
-        <v>1.26473045349121</v>
+        <v>1.2647305727005</v>
       </c>
       <c r="H539" t="n">
         <v>89519</v>
@@ -16029,7 +16029,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G540" t="n">
-        <v>1.24666285514832</v>
+        <v>1.24666273593903</v>
       </c>
       <c r="H540" t="n">
         <v>41314</v>
@@ -16058,7 +16058,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G541" t="n">
-        <v>1.27557110786438</v>
+        <v>1.27557098865509</v>
       </c>
       <c r="H541" t="n">
         <v>65278</v>
@@ -16087,7 +16087,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G542" t="n">
-        <v>1.27195763587952</v>
+        <v>1.27195739746094</v>
       </c>
       <c r="H542" t="n">
         <v>14840</v>
@@ -16203,7 +16203,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G546" t="n">
-        <v>1.30086553096771</v>
+        <v>1.300865650177</v>
       </c>
       <c r="H546" t="n">
         <v>68871</v>
@@ -16232,7 +16232,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G547" t="n">
-        <v>1.28279793262482</v>
+        <v>1.28279805183411</v>
       </c>
       <c r="H547" t="n">
         <v>6756</v>
@@ -16261,7 +16261,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G548" t="n">
-        <v>1.27195763587952</v>
+        <v>1.27195739746094</v>
       </c>
       <c r="H548" t="n">
         <v>42808</v>
@@ -16348,7 +16348,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G551" t="n">
-        <v>1.27195763587952</v>
+        <v>1.27195739746094</v>
       </c>
       <c r="H551" t="n">
         <v>4210</v>
@@ -16377,7 +16377,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G552" t="n">
-        <v>1.25027644634247</v>
+        <v>1.25027656555176</v>
       </c>
       <c r="H552" t="n">
         <v>27955</v>
@@ -16406,7 +16406,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G553" t="n">
-        <v>1.25750350952148</v>
+        <v>1.25750339031219</v>
       </c>
       <c r="H553" t="n">
         <v>22811</v>
@@ -16435,7 +16435,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G554" t="n">
-        <v>1.25750350952148</v>
+        <v>1.25750339031219</v>
       </c>
       <c r="H554" t="n">
         <v>38328</v>
@@ -16493,7 +16493,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G556" t="n">
-        <v>1.25389015674591</v>
+        <v>1.25389003753662</v>
       </c>
       <c r="H556" t="n">
         <v>38870</v>
@@ -16522,7 +16522,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G557" t="n">
-        <v>1.25389015674591</v>
+        <v>1.25389003753662</v>
       </c>
       <c r="H557" t="n">
         <v>7016</v>
@@ -16551,7 +16551,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G558" t="n">
-        <v>1.25027644634247</v>
+        <v>1.25027656555176</v>
       </c>
       <c r="H558" t="n">
         <v>6400</v>
@@ -16580,7 +16580,7 @@
         <v>1.75</v>
       </c>
       <c r="G559" t="n">
-        <v>1.26473045349121</v>
+        <v>1.2647305727005</v>
       </c>
       <c r="H559" t="n">
         <v>9625</v>
@@ -16609,7 +16609,7 @@
         <v>1.75</v>
       </c>
       <c r="G560" t="n">
-        <v>1.26473045349121</v>
+        <v>1.2647305727005</v>
       </c>
       <c r="H560" t="n">
         <v>10249</v>
@@ -16638,7 +16638,7 @@
         <v>1.75</v>
       </c>
       <c r="G561" t="n">
-        <v>1.26473045349121</v>
+        <v>1.2647305727005</v>
       </c>
       <c r="H561" t="n">
         <v>20600</v>
@@ -16754,7 +16754,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G565" t="n">
-        <v>1.32977390289307</v>
+        <v>1.32977366447449</v>
       </c>
       <c r="H565" t="n">
         <v>25667</v>
@@ -16783,7 +16783,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G566" t="n">
-        <v>1.34061431884766</v>
+        <v>1.34061443805695</v>
       </c>
       <c r="H566" t="n">
         <v>16417</v>
@@ -16812,7 +16812,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G567" t="n">
-        <v>1.3370007276535</v>
+        <v>1.33700084686279</v>
       </c>
       <c r="H567" t="n">
         <v>12710</v>
@@ -16899,7 +16899,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G570" t="n">
-        <v>1.35145497322083</v>
+        <v>1.35145485401154</v>
       </c>
       <c r="H570" t="n">
         <v>34743</v>
@@ -16957,7 +16957,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G572" t="n">
-        <v>1.36590886116028</v>
+        <v>1.36590898036957</v>
       </c>
       <c r="H572" t="n">
         <v>19725</v>
@@ -17102,7 +17102,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G577" t="n">
-        <v>1.39843046665192</v>
+        <v>1.39843058586121</v>
       </c>
       <c r="H577" t="n">
         <v>14994</v>
@@ -17131,7 +17131,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G578" t="n">
-        <v>1.41649830341339</v>
+        <v>1.4164981842041</v>
       </c>
       <c r="H578" t="n">
         <v>14135</v>
@@ -17218,7 +17218,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G581" t="n">
-        <v>1.42733883857727</v>
+        <v>1.42733871936798</v>
       </c>
       <c r="H581" t="n">
         <v>31790</v>
@@ -17247,7 +17247,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G582" t="n">
-        <v>1.39481687545776</v>
+        <v>1.39481699466705</v>
       </c>
       <c r="H582" t="n">
         <v>13900</v>
@@ -17305,7 +17305,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G584" t="n">
-        <v>1.36952221393585</v>
+        <v>1.36952245235443</v>
       </c>
       <c r="H584" t="n">
         <v>16535</v>
@@ -17334,7 +17334,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G585" t="n">
-        <v>1.38759005069733</v>
+        <v>1.38758993148804</v>
       </c>
       <c r="H585" t="n">
         <v>5959</v>
@@ -17363,7 +17363,7 @@
         <v>1.875</v>
       </c>
       <c r="G586" t="n">
-        <v>1.3550683259964</v>
+        <v>1.35506844520569</v>
       </c>
       <c r="H586" t="n">
         <v>32000</v>
@@ -17450,7 +17450,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G589" t="n">
-        <v>1.34784150123596</v>
+        <v>1.34784126281738</v>
       </c>
       <c r="H589" t="n">
         <v>12022</v>
@@ -17508,7 +17508,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G591" t="n">
-        <v>1.36590886116028</v>
+        <v>1.36590898036957</v>
       </c>
       <c r="H591" t="n">
         <v>19988</v>
@@ -17537,7 +17537,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G592" t="n">
-        <v>1.36590886116028</v>
+        <v>1.36590898036957</v>
       </c>
       <c r="H592" t="n">
         <v>35497</v>
@@ -17566,7 +17566,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G593" t="n">
-        <v>1.36590886116028</v>
+        <v>1.36590898036957</v>
       </c>
       <c r="H593" t="n">
         <v>25800</v>
@@ -17682,7 +17682,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G597" t="n">
-        <v>1.34784150123596</v>
+        <v>1.34784126281738</v>
       </c>
       <c r="H597" t="n">
         <v>16261</v>
@@ -17711,7 +17711,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G598" t="n">
-        <v>1.3370007276535</v>
+        <v>1.33700084686279</v>
       </c>
       <c r="H598" t="n">
         <v>28424</v>
@@ -17769,7 +17769,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G600" t="n">
-        <v>1.34061431884766</v>
+        <v>1.34061443805695</v>
       </c>
       <c r="H600" t="n">
         <v>25336</v>
@@ -17943,7 +17943,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G606" t="n">
-        <v>1.36590886116028</v>
+        <v>1.36590898036957</v>
       </c>
       <c r="H606" t="n">
         <v>37284</v>
@@ -18030,7 +18030,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G609" t="n">
-        <v>1.3370007276535</v>
+        <v>1.33700084686279</v>
       </c>
       <c r="H609" t="n">
         <v>18356</v>
@@ -18059,7 +18059,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G610" t="n">
-        <v>1.3370007276535</v>
+        <v>1.33700084686279</v>
       </c>
       <c r="H610" t="n">
         <v>2030</v>
@@ -18117,7 +18117,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G612" t="n">
-        <v>1.3370007276535</v>
+        <v>1.33700084686279</v>
       </c>
       <c r="H612" t="n">
         <v>11851</v>
@@ -18146,7 +18146,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G613" t="n">
-        <v>1.30086553096771</v>
+        <v>1.300865650177</v>
       </c>
       <c r="H613" t="n">
         <v>35985</v>
@@ -18175,7 +18175,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G614" t="n">
-        <v>1.22859537601471</v>
+        <v>1.22859525680542</v>
       </c>
       <c r="H614" t="n">
         <v>110352</v>
@@ -18204,7 +18204,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G615" t="n">
-        <v>1.24666285514832</v>
+        <v>1.24666273593903</v>
       </c>
       <c r="H615" t="n">
         <v>11921</v>
@@ -18233,7 +18233,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G616" t="n">
-        <v>1.24666285514832</v>
+        <v>1.24666273593903</v>
       </c>
       <c r="H616" t="n">
         <v>27753</v>
@@ -18349,7 +18349,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G620" t="n">
-        <v>1.35145497322083</v>
+        <v>1.35145485401154</v>
       </c>
       <c r="H620" t="n">
         <v>62899</v>
@@ -18378,7 +18378,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G621" t="n">
-        <v>1.39481687545776</v>
+        <v>1.39481699466705</v>
       </c>
       <c r="H621" t="n">
         <v>238374</v>
@@ -18407,7 +18407,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G622" t="n">
-        <v>1.38759005069733</v>
+        <v>1.38758993148804</v>
       </c>
       <c r="H622" t="n">
         <v>232409</v>
@@ -18552,7 +18552,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G627" t="n">
-        <v>1.45263338088989</v>
+        <v>1.45263314247131</v>
       </c>
       <c r="H627" t="n">
         <v>88829</v>
@@ -18581,7 +18581,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G628" t="n">
-        <v>1.45263338088989</v>
+        <v>1.45263314247131</v>
       </c>
       <c r="H628" t="n">
         <v>36347</v>
@@ -18668,7 +18668,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G631" t="n">
-        <v>1.40204429626465</v>
+        <v>1.40204417705536</v>
       </c>
       <c r="H631" t="n">
         <v>31234</v>
@@ -18755,7 +18755,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>1.41649830341339</v>
+        <v>1.4164981842041</v>
       </c>
       <c r="H634" t="n">
         <v>3390</v>
@@ -18784,7 +18784,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G635" t="n">
-        <v>1.42733883857727</v>
+        <v>1.42733871936798</v>
       </c>
       <c r="H635" t="n">
         <v>1450</v>
@@ -18813,7 +18813,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G636" t="n">
-        <v>1.41649830341339</v>
+        <v>1.4164981842041</v>
       </c>
       <c r="H636" t="n">
         <v>37192</v>
@@ -18842,7 +18842,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G637" t="n">
-        <v>1.42733883857727</v>
+        <v>1.42733871936798</v>
       </c>
       <c r="H637" t="n">
         <v>16867</v>
@@ -18871,7 +18871,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G638" t="n">
-        <v>1.42733883857727</v>
+        <v>1.42733871936798</v>
       </c>
       <c r="H638" t="n">
         <v>8301</v>
@@ -18929,7 +18929,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G640" t="n">
-        <v>1.42733883857727</v>
+        <v>1.42733871936798</v>
       </c>
       <c r="H640" t="n">
         <v>9400</v>
@@ -18958,7 +18958,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G641" t="n">
-        <v>1.42733883857727</v>
+        <v>1.42733871936798</v>
       </c>
       <c r="H641" t="n">
         <v>7045</v>
@@ -19045,7 +19045,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G644" t="n">
-        <v>1.40204429626465</v>
+        <v>1.40204417705536</v>
       </c>
       <c r="H644" t="n">
         <v>41217</v>
@@ -19103,7 +19103,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G646" t="n">
-        <v>1.41649830341339</v>
+        <v>1.4164981842041</v>
       </c>
       <c r="H646" t="n">
         <v>9428</v>
@@ -19132,7 +19132,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G647" t="n">
-        <v>1.42733883857727</v>
+        <v>1.42733871936798</v>
       </c>
       <c r="H647" t="n">
         <v>11933</v>
@@ -19161,7 +19161,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G648" t="n">
-        <v>1.41649830341339</v>
+        <v>1.4164981842041</v>
       </c>
       <c r="H648" t="n">
         <v>12525</v>
@@ -19190,7 +19190,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>1.41649830341339</v>
+        <v>1.4164981842041</v>
       </c>
       <c r="H649" t="n">
         <v>0</v>
@@ -19335,7 +19335,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G654" t="n">
-        <v>1.42733883857727</v>
+        <v>1.42733871936798</v>
       </c>
       <c r="H654" t="n">
         <v>5365</v>
@@ -19364,7 +19364,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.40204429626465</v>
+        <v>1.40204417705536</v>
       </c>
       <c r="H655" t="n">
         <v>26510</v>
@@ -19393,7 +19393,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G656" t="n">
-        <v>1.38759005069733</v>
+        <v>1.38758993148804</v>
       </c>
       <c r="H656" t="n">
         <v>40388</v>
@@ -19451,7 +19451,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>1.41288447380066</v>
+        <v>1.41288459300995</v>
       </c>
       <c r="H658" t="n">
         <v>23918</v>
@@ -19712,7 +19712,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G667" t="n">
-        <v>1.4203405380249</v>
+        <v>1.42034041881561</v>
       </c>
       <c r="H667" t="n">
         <v>32416</v>
@@ -19741,7 +19741,7 @@
         <v>1.875</v>
       </c>
       <c r="G668" t="n">
-        <v>1.39797294139862</v>
+        <v>1.39797282218933</v>
       </c>
       <c r="H668" t="n">
         <v>21406</v>
@@ -19770,7 +19770,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G669" t="n">
-        <v>1.40915668010712</v>
+        <v>1.40915679931641</v>
       </c>
       <c r="H669" t="n">
         <v>415</v>
@@ -19799,7 +19799,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G670" t="n">
-        <v>1.39051723480225</v>
+        <v>1.39051711559296</v>
       </c>
       <c r="H670" t="n">
         <v>1000</v>
@@ -19828,7 +19828,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G671" t="n">
-        <v>1.37933325767517</v>
+        <v>1.37933337688446</v>
       </c>
       <c r="H671" t="n">
         <v>22600</v>
@@ -19857,7 +19857,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G672" t="n">
-        <v>1.4203405380249</v>
+        <v>1.42034041881561</v>
       </c>
       <c r="H672" t="n">
         <v>10110</v>
@@ -19915,7 +19915,7 @@
         <v>1.875</v>
       </c>
       <c r="G674" t="n">
-        <v>1.39797294139862</v>
+        <v>1.39797282218933</v>
       </c>
       <c r="H674" t="n">
         <v>4500</v>
@@ -19973,7 +19973,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G676" t="n">
-        <v>1.40915668010712</v>
+        <v>1.40915679931641</v>
       </c>
       <c r="H676" t="n">
         <v>17019</v>
@@ -20002,7 +20002,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G677" t="n">
-        <v>1.40170085430145</v>
+        <v>1.40170073509216</v>
       </c>
       <c r="H677" t="n">
         <v>641</v>
@@ -20060,7 +20060,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G679" t="n">
-        <v>1.40915668010712</v>
+        <v>1.40915679931641</v>
       </c>
       <c r="H679" t="n">
         <v>14000</v>
@@ -20089,7 +20089,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G680" t="n">
-        <v>1.40915668010712</v>
+        <v>1.40915679931641</v>
       </c>
       <c r="H680" t="n">
         <v>2136</v>
@@ -20176,7 +20176,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G683" t="n">
-        <v>1.29731893539429</v>
+        <v>1.297318816185</v>
       </c>
       <c r="H683" t="n">
         <v>79982</v>
@@ -20205,7 +20205,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G684" t="n">
-        <v>1.34205389022827</v>
+        <v>1.34205412864685</v>
       </c>
       <c r="H684" t="n">
         <v>32518</v>
@@ -20234,7 +20234,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G685" t="n">
-        <v>1.37933325767517</v>
+        <v>1.37933337688446</v>
       </c>
       <c r="H685" t="n">
         <v>18544</v>
@@ -20263,7 +20263,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G686" t="n">
-        <v>1.35323786735535</v>
+        <v>1.35323798656464</v>
       </c>
       <c r="H686" t="n">
         <v>2092</v>
@@ -20292,7 +20292,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G687" t="n">
-        <v>1.37933325767517</v>
+        <v>1.37933337688446</v>
       </c>
       <c r="H687" t="n">
         <v>7671</v>
@@ -20321,7 +20321,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G688" t="n">
-        <v>1.39051723480225</v>
+        <v>1.39051711559296</v>
       </c>
       <c r="H688" t="n">
         <v>8059</v>
@@ -20350,7 +20350,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G689" t="n">
-        <v>1.36069357395172</v>
+        <v>1.36069369316101</v>
       </c>
       <c r="H689" t="n">
         <v>7448</v>
@@ -20379,7 +20379,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G690" t="n">
-        <v>1.36442172527313</v>
+        <v>1.36442160606384</v>
       </c>
       <c r="H690" t="n">
         <v>3361</v>
@@ -20437,7 +20437,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G692" t="n">
-        <v>1.37933325767517</v>
+        <v>1.37933337688446</v>
       </c>
       <c r="H692" t="n">
         <v>20364</v>
@@ -20466,7 +20466,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G693" t="n">
-        <v>1.37933325767517</v>
+        <v>1.37933337688446</v>
       </c>
       <c r="H693" t="n">
         <v>50</v>
@@ -20524,7 +20524,7 @@
         <v>1.875</v>
       </c>
       <c r="G695" t="n">
-        <v>1.39797294139862</v>
+        <v>1.39797282218933</v>
       </c>
       <c r="H695" t="n">
         <v>5638</v>
@@ -20553,7 +20553,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G696" t="n">
-        <v>1.40170085430145</v>
+        <v>1.40170073509216</v>
       </c>
       <c r="H696" t="n">
         <v>7317</v>
@@ -20611,7 +20611,7 @@
         <v>1.875</v>
       </c>
       <c r="G698" t="n">
-        <v>1.39797294139862</v>
+        <v>1.39797282218933</v>
       </c>
       <c r="H698" t="n">
         <v>5004</v>
@@ -20640,7 +20640,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G699" t="n">
-        <v>1.37933325767517</v>
+        <v>1.37933337688446</v>
       </c>
       <c r="H699" t="n">
         <v>2361</v>
@@ -20756,7 +20756,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G703" t="n">
-        <v>1.34205389022827</v>
+        <v>1.34205412864685</v>
       </c>
       <c r="H703" t="n">
         <v>55874</v>
@@ -20814,7 +20814,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G705" t="n">
-        <v>1.32714223861694</v>
+        <v>1.32714235782623</v>
       </c>
       <c r="H705" t="n">
         <v>4994</v>
@@ -20843,7 +20843,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G706" t="n">
-        <v>1.32714223861694</v>
+        <v>1.32714235782623</v>
       </c>
       <c r="H706" t="n">
         <v>31734</v>
@@ -20872,7 +20872,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G707" t="n">
-        <v>1.28240728378296</v>
+        <v>1.28240716457367</v>
       </c>
       <c r="H707" t="n">
         <v>45087</v>
@@ -20901,7 +20901,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G708" t="n">
-        <v>1.26003956794739</v>
+        <v>1.26003968715668</v>
       </c>
       <c r="H708" t="n">
         <v>25623</v>
@@ -20930,7 +20930,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G709" t="n">
-        <v>1.26003956794739</v>
+        <v>1.26003968715668</v>
       </c>
       <c r="H709" t="n">
         <v>13002</v>
@@ -20988,7 +20988,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.27495133876801</v>
+        <v>1.27495145797729</v>
       </c>
       <c r="H711" t="n">
         <v>9284</v>
@@ -21046,7 +21046,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G713" t="n">
-        <v>1.27495133876801</v>
+        <v>1.27495145797729</v>
       </c>
       <c r="H713" t="n">
         <v>5689</v>
@@ -21191,7 +21191,7 @@
         <v>1.65499997138977</v>
       </c>
       <c r="G718" t="n">
-        <v>1.23394417762756</v>
+        <v>1.23394405841827</v>
       </c>
       <c r="H718" t="n">
         <v>2500</v>
@@ -21249,7 +21249,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G720" t="n">
-        <v>1.26003956794739</v>
+        <v>1.26003968715668</v>
       </c>
       <c r="H720" t="n">
         <v>4576</v>
@@ -21336,7 +21336,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G723" t="n">
-        <v>1.26003956794739</v>
+        <v>1.26003968715668</v>
       </c>
       <c r="H723" t="n">
         <v>3000</v>
@@ -21365,7 +21365,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G724" t="n">
-        <v>1.27495133876801</v>
+        <v>1.27495145797729</v>
       </c>
       <c r="H724" t="n">
         <v>5300</v>
@@ -21394,7 +21394,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>1.27495133876801</v>
+        <v>1.27495145797729</v>
       </c>
       <c r="H725" t="n">
         <v>4500</v>
@@ -21423,7 +21423,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G726" t="n">
-        <v>1.28240728378296</v>
+        <v>1.28240716457367</v>
       </c>
       <c r="H726" t="n">
         <v>1750</v>
@@ -21481,7 +21481,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>1.31968653202057</v>
+        <v>1.31968641281128</v>
       </c>
       <c r="H728" t="n">
         <v>24193</v>
@@ -21510,7 +21510,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G729" t="n">
-        <v>1.33832609653473</v>
+        <v>1.33832597732544</v>
       </c>
       <c r="H729" t="n">
         <v>2960</v>
@@ -21539,7 +21539,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G730" t="n">
-        <v>1.34205389022827</v>
+        <v>1.34205412864685</v>
       </c>
       <c r="H730" t="n">
         <v>10785</v>
@@ -21568,7 +21568,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G731" t="n">
-        <v>1.34205389022827</v>
+        <v>1.34205412864685</v>
       </c>
       <c r="H731" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G734" t="n">
-        <v>1.29731893539429</v>
+        <v>1.297318816185</v>
       </c>
       <c r="H734" t="n">
         <v>5437</v>
@@ -21713,7 +21713,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G736" t="n">
-        <v>1.26376760005951</v>
+        <v>1.26376748085022</v>
       </c>
       <c r="H736" t="n">
         <v>25907</v>
@@ -21742,7 +21742,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G737" t="n">
-        <v>1.27495133876801</v>
+        <v>1.27495145797729</v>
       </c>
       <c r="H737" t="n">
         <v>25500</v>
@@ -21829,7 +21829,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G740" t="n">
-        <v>1.34205389022827</v>
+        <v>1.34205412864685</v>
       </c>
       <c r="H740" t="n">
         <v>79775</v>
@@ -21858,7 +21858,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G741" t="n">
-        <v>1.32714223861694</v>
+        <v>1.32714235782623</v>
       </c>
       <c r="H741" t="n">
         <v>39398</v>
@@ -21887,7 +21887,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G742" t="n">
-        <v>1.34205389022827</v>
+        <v>1.34205412864685</v>
       </c>
       <c r="H742" t="n">
         <v>25469</v>
@@ -21945,7 +21945,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G744" t="n">
-        <v>1.32714223861694</v>
+        <v>1.32714235782623</v>
       </c>
       <c r="H744" t="n">
         <v>2676</v>
@@ -22003,7 +22003,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G746" t="n">
-        <v>1.33832609653473</v>
+        <v>1.33832597732544</v>
       </c>
       <c r="H746" t="n">
         <v>22245</v>
@@ -22032,7 +22032,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G747" t="n">
-        <v>1.35323786735535</v>
+        <v>1.35323798656464</v>
       </c>
       <c r="H747" t="n">
         <v>26580</v>
@@ -22235,7 +22235,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G754" t="n">
-        <v>1.2376720905304</v>
+        <v>1.23767197132111</v>
       </c>
       <c r="H754" t="n">
         <v>13729</v>
@@ -22264,7 +22264,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G755" t="n">
-        <v>1.27122330665588</v>
+        <v>1.27122342586517</v>
       </c>
       <c r="H755" t="n">
         <v>25092</v>
@@ -22293,7 +22293,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G756" t="n">
-        <v>1.23021638393402</v>
+        <v>1.23021614551544</v>
       </c>
       <c r="H756" t="n">
         <v>17510</v>
@@ -22322,7 +22322,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G757" t="n">
-        <v>1.22276020050049</v>
+        <v>1.22276031970978</v>
       </c>
       <c r="H757" t="n">
         <v>13785</v>
@@ -22351,7 +22351,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G758" t="n">
-        <v>1.23021638393402</v>
+        <v>1.23021614551544</v>
       </c>
       <c r="H758" t="n">
         <v>16510</v>
@@ -22380,7 +22380,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G759" t="n">
-        <v>1.25258374214172</v>
+        <v>1.25258362293243</v>
       </c>
       <c r="H759" t="n">
         <v>18688</v>
@@ -22409,7 +22409,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G760" t="n">
-        <v>1.26376760005951</v>
+        <v>1.26376748085022</v>
       </c>
       <c r="H760" t="n">
         <v>27620</v>
@@ -22438,7 +22438,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G761" t="n">
-        <v>1.26376760005951</v>
+        <v>1.26376748085022</v>
       </c>
       <c r="H761" t="n">
         <v>49084</v>
@@ -22554,7 +22554,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G765" t="n">
-        <v>1.28240728378296</v>
+        <v>1.28240716457367</v>
       </c>
       <c r="H765" t="n">
         <v>15892</v>
@@ -22641,7 +22641,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G768" t="n">
-        <v>1.31968653202057</v>
+        <v>1.31968641281128</v>
       </c>
       <c r="H768" t="n">
         <v>103625</v>
@@ -22670,7 +22670,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G769" t="n">
-        <v>1.29731893539429</v>
+        <v>1.297318816185</v>
       </c>
       <c r="H769" t="n">
         <v>20113</v>
@@ -22757,7 +22757,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G772" t="n">
-        <v>1.28240728378296</v>
+        <v>1.28240716457367</v>
       </c>
       <c r="H772" t="n">
         <v>7240</v>
@@ -22989,7 +22989,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G780" t="n">
-        <v>1.35323786735535</v>
+        <v>1.35323798656464</v>
       </c>
       <c r="H780" t="n">
         <v>21228</v>
@@ -23018,7 +23018,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G781" t="n">
-        <v>1.34950971603394</v>
+        <v>1.34950983524323</v>
       </c>
       <c r="H781" t="n">
         <v>11749</v>
@@ -23047,7 +23047,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G782" t="n">
-        <v>1.35323786735535</v>
+        <v>1.35323798656464</v>
       </c>
       <c r="H782" t="n">
         <v>29358</v>
@@ -23163,7 +23163,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G786" t="n">
-        <v>1.36069357395172</v>
+        <v>1.36069369316101</v>
       </c>
       <c r="H786" t="n">
         <v>9809</v>
@@ -23192,7 +23192,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G787" t="n">
-        <v>1.36442172527313</v>
+        <v>1.36442160606384</v>
       </c>
       <c r="H787" t="n">
         <v>6222</v>
@@ -23221,7 +23221,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G788" t="n">
-        <v>1.36442172527313</v>
+        <v>1.36442160606384</v>
       </c>
       <c r="H788" t="n">
         <v>9845</v>
@@ -23250,7 +23250,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G789" t="n">
-        <v>1.34950971603394</v>
+        <v>1.34950983524323</v>
       </c>
       <c r="H789" t="n">
         <v>40415</v>
@@ -23279,7 +23279,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G790" t="n">
-        <v>1.4203405380249</v>
+        <v>1.42034041881561</v>
       </c>
       <c r="H790" t="n">
         <v>333049</v>
@@ -23308,7 +23308,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G791" t="n">
-        <v>1.41661250591278</v>
+        <v>1.41661238670349</v>
       </c>
       <c r="H791" t="n">
         <v>161936</v>
@@ -23366,7 +23366,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G793" t="n">
-        <v>1.40170085430145</v>
+        <v>1.40170073509216</v>
       </c>
       <c r="H793" t="n">
         <v>15800</v>
@@ -23424,7 +23424,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G795" t="n">
-        <v>1.41661250591278</v>
+        <v>1.41661238670349</v>
       </c>
       <c r="H795" t="n">
         <v>215545</v>
@@ -23453,7 +23453,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G796" t="n">
-        <v>1.41661250591278</v>
+        <v>1.41661238670349</v>
       </c>
       <c r="H796" t="n">
         <v>5816</v>
@@ -23482,7 +23482,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G797" t="n">
-        <v>1.4203405380249</v>
+        <v>1.42034041881561</v>
       </c>
       <c r="H797" t="n">
         <v>41974</v>
@@ -23540,7 +23540,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G799" t="n">
-        <v>1.4203405380249</v>
+        <v>1.42034041881561</v>
       </c>
       <c r="H799" t="n">
         <v>176400</v>
@@ -23743,7 +23743,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G806" t="n">
-        <v>1.47625935077667</v>
+        <v>1.47625946998596</v>
       </c>
       <c r="H806" t="n">
         <v>64617</v>
@@ -23772,7 +23772,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G807" t="n">
-        <v>1.52099442481995</v>
+        <v>1.52099454402924</v>
       </c>
       <c r="H807" t="n">
         <v>125438</v>
@@ -23801,7 +23801,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G808" t="n">
-        <v>1.51353859901428</v>
+        <v>1.51353871822357</v>
       </c>
       <c r="H808" t="n">
         <v>43051</v>
@@ -23830,7 +23830,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G809" t="n">
-        <v>1.51353859901428</v>
+        <v>1.51353871822357</v>
       </c>
       <c r="H809" t="n">
         <v>209167</v>
@@ -23859,7 +23859,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G810" t="n">
-        <v>1.54336202144623</v>
+        <v>1.54336214065552</v>
       </c>
       <c r="H810" t="n">
         <v>74409</v>
@@ -23917,7 +23917,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G812" t="n">
-        <v>1.53590631484985</v>
+        <v>1.53590619564056</v>
       </c>
       <c r="H812" t="n">
         <v>27473</v>
@@ -23946,7 +23946,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>1.52099442481995</v>
+        <v>1.52099454402924</v>
       </c>
       <c r="H813" t="n">
         <v>25496</v>
@@ -23975,7 +23975,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G814" t="n">
-        <v>1.53590631484985</v>
+        <v>1.53590619564056</v>
       </c>
       <c r="H814" t="n">
         <v>10381</v>
@@ -24004,7 +24004,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>1.50608289241791</v>
+        <v>1.50608277320862</v>
       </c>
       <c r="H815" t="n">
         <v>32747</v>
@@ -24033,7 +24033,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G816" t="n">
-        <v>1.55081808567047</v>
+        <v>1.55081796646118</v>
       </c>
       <c r="H816" t="n">
         <v>46477</v>
@@ -24062,7 +24062,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G817" t="n">
-        <v>1.53590631484985</v>
+        <v>1.53590619564056</v>
       </c>
       <c r="H817" t="n">
         <v>111089</v>
@@ -24178,7 +24178,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G821" t="n">
-        <v>1.53590631484985</v>
+        <v>1.53590619564056</v>
       </c>
       <c r="H821" t="n">
         <v>49834</v>
@@ -24207,7 +24207,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G822" t="n">
-        <v>1.52099442481995</v>
+        <v>1.52099454402924</v>
       </c>
       <c r="H822" t="n">
         <v>13449</v>
@@ -24236,7 +24236,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G823" t="n">
-        <v>1.53590631484985</v>
+        <v>1.53590619564056</v>
       </c>
       <c r="H823" t="n">
         <v>20847</v>
@@ -24294,7 +24294,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G825" t="n">
-        <v>1.55081808567047</v>
+        <v>1.55081796646118</v>
       </c>
       <c r="H825" t="n">
         <v>23013</v>
@@ -24352,7 +24352,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G827" t="n">
-        <v>1.54336202144623</v>
+        <v>1.54336214065552</v>
       </c>
       <c r="H827" t="n">
         <v>7778</v>
@@ -24410,7 +24410,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G829" t="n">
-        <v>1.57318544387817</v>
+        <v>1.57318532466888</v>
       </c>
       <c r="H829" t="n">
         <v>28439</v>
@@ -24468,7 +24468,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G831" t="n">
-        <v>1.53590631484985</v>
+        <v>1.53590619564056</v>
       </c>
       <c r="H831" t="n">
         <v>41750</v>
@@ -24526,7 +24526,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G833" t="n">
-        <v>1.55081808567047</v>
+        <v>1.55081796646118</v>
       </c>
       <c r="H833" t="n">
         <v>115673</v>
@@ -24555,7 +24555,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G834" t="n">
-        <v>1.55081808567047</v>
+        <v>1.55081796646118</v>
       </c>
       <c r="H834" t="n">
         <v>21411</v>
@@ -24584,7 +24584,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G835" t="n">
-        <v>1.55081808567047</v>
+        <v>1.55081796646118</v>
       </c>
       <c r="H835" t="n">
         <v>57106</v>
@@ -24700,7 +24700,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G839" t="n">
-        <v>1.53590631484985</v>
+        <v>1.53590619564056</v>
       </c>
       <c r="H839" t="n">
         <v>108358</v>
@@ -24729,7 +24729,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G840" t="n">
-        <v>1.54336202144623</v>
+        <v>1.54336214065552</v>
       </c>
       <c r="H840" t="n">
         <v>14729</v>
@@ -24874,7 +24874,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G845" t="n">
-        <v>1.58064138889313</v>
+        <v>1.58064126968384</v>
       </c>
       <c r="H845" t="n">
         <v>296080</v>
@@ -24903,7 +24903,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G846" t="n">
-        <v>1.57318544387817</v>
+        <v>1.57318532466888</v>
       </c>
       <c r="H846" t="n">
         <v>26955</v>
@@ -24932,7 +24932,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G847" t="n">
-        <v>1.58064138889313</v>
+        <v>1.58064126968384</v>
       </c>
       <c r="H847" t="n">
         <v>29419</v>
@@ -24961,7 +24961,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G848" t="n">
-        <v>1.58809757232666</v>
+        <v>1.58809733390808</v>
       </c>
       <c r="H848" t="n">
         <v>7824</v>
@@ -24990,7 +24990,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G849" t="n">
-        <v>1.55081808567047</v>
+        <v>1.55081796646118</v>
       </c>
       <c r="H849" t="n">
         <v>12181</v>
@@ -25077,7 +25077,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>1.55081808567047</v>
+        <v>1.55081796646118</v>
       </c>
       <c r="H852" t="n">
         <v>32993</v>
@@ -25135,7 +25135,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G854" t="n">
-        <v>1.54336202144623</v>
+        <v>1.54336214065552</v>
       </c>
       <c r="H854" t="n">
         <v>37885</v>
@@ -25193,7 +25193,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G856" t="n">
-        <v>1.53590631484985</v>
+        <v>1.53590619564056</v>
       </c>
       <c r="H856" t="n">
         <v>42772</v>
@@ -25222,7 +25222,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G857" t="n">
-        <v>1.57318544387817</v>
+        <v>1.57318532466888</v>
       </c>
       <c r="H857" t="n">
         <v>9893</v>
@@ -25251,7 +25251,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G858" t="n">
-        <v>1.54336202144623</v>
+        <v>1.54336214065552</v>
       </c>
       <c r="H858" t="n">
         <v>5417</v>
@@ -25309,7 +25309,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G860" t="n">
-        <v>1.62537670135498</v>
+        <v>1.6253764629364</v>
       </c>
       <c r="H860" t="n">
         <v>323391</v>
@@ -25338,7 +25338,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G861" t="n">
-        <v>1.67011165618896</v>
+        <v>1.67011153697968</v>
       </c>
       <c r="H861" t="n">
         <v>178995</v>
@@ -25367,7 +25367,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>1.66265594959259</v>
+        <v>1.6626558303833</v>
       </c>
       <c r="H862" t="n">
         <v>204589</v>
@@ -25454,7 +25454,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G865" t="n">
-        <v>1.7595819234848</v>
+        <v>1.75958180427551</v>
       </c>
       <c r="H865" t="n">
         <v>267822</v>
@@ -25483,7 +25483,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G866" t="n">
-        <v>1.7595819234848</v>
+        <v>1.75958180427551</v>
       </c>
       <c r="H866" t="n">
         <v>79344</v>
@@ -25512,7 +25512,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G867" t="n">
-        <v>1.7595819234848</v>
+        <v>1.75958180427551</v>
       </c>
       <c r="H867" t="n">
         <v>28147</v>
@@ -25541,7 +25541,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G868" t="n">
-        <v>1.68502330780029</v>
+        <v>1.68502354621887</v>
       </c>
       <c r="H868" t="n">
         <v>97192</v>
@@ -25744,7 +25744,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G875" t="n">
-        <v>1.7446700334549</v>
+        <v>1.74467027187347</v>
       </c>
       <c r="H875" t="n">
         <v>121208</v>
@@ -25773,7 +25773,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G876" t="n">
-        <v>1.75212609767914</v>
+        <v>1.75212621688843</v>
       </c>
       <c r="H876" t="n">
         <v>83367</v>
@@ -25802,7 +25802,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G877" t="n">
-        <v>1.7446700334549</v>
+        <v>1.74467027187347</v>
       </c>
       <c r="H877" t="n">
         <v>18243</v>
@@ -25889,7 +25889,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G880" t="n">
-        <v>1.78940558433533</v>
+        <v>1.78940534591675</v>
       </c>
       <c r="H880" t="n">
         <v>369359</v>
@@ -25918,7 +25918,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G881" t="n">
-        <v>1.78194963932037</v>
+        <v>1.78194975852966</v>
       </c>
       <c r="H881" t="n">
         <v>58177</v>
@@ -26005,7 +26005,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G884" t="n">
-        <v>1.75212609767914</v>
+        <v>1.75212621688843</v>
       </c>
       <c r="H884" t="n">
         <v>62126</v>
@@ -26121,7 +26121,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G888" t="n">
-        <v>1.78940558433533</v>
+        <v>1.78940534591675</v>
       </c>
       <c r="H888" t="n">
         <v>119995</v>
@@ -26150,7 +26150,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G889" t="n">
-        <v>1.7595819234848</v>
+        <v>1.75958180427551</v>
       </c>
       <c r="H889" t="n">
         <v>22356</v>
@@ -26179,7 +26179,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G890" t="n">
-        <v>1.78940558433533</v>
+        <v>1.78940534591675</v>
       </c>
       <c r="H890" t="n">
         <v>49724</v>
@@ -26208,7 +26208,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G891" t="n">
-        <v>1.84905219078064</v>
+        <v>1.84905242919922</v>
       </c>
       <c r="H891" t="n">
         <v>211597</v>
@@ -26353,7 +26353,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G896" t="n">
-        <v>1.87887561321259</v>
+        <v>1.87887585163116</v>
       </c>
       <c r="H896" t="n">
         <v>96456</v>
@@ -26440,7 +26440,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G899" t="n">
-        <v>1.87141954898834</v>
+        <v>1.87141978740692</v>
       </c>
       <c r="H899" t="n">
         <v>101675</v>
@@ -26498,7 +26498,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G901" t="n">
-        <v>1.84159636497498</v>
+        <v>1.84159660339355</v>
       </c>
       <c r="H901" t="n">
         <v>18388</v>
@@ -26585,7 +26585,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G904" t="n">
-        <v>1.82668483257294</v>
+        <v>1.82668459415436</v>
       </c>
       <c r="H904" t="n">
         <v>33139</v>
@@ -26643,7 +26643,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>1.82668483257294</v>
+        <v>1.82668459415436</v>
       </c>
       <c r="H906" t="n">
         <v>55005</v>
@@ -26672,7 +26672,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G907" t="n">
-        <v>1.87887561321259</v>
+        <v>1.87887585163116</v>
       </c>
       <c r="H907" t="n">
         <v>119402</v>
@@ -26701,7 +26701,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G908" t="n">
-        <v>1.87887561321259</v>
+        <v>1.87887585163116</v>
       </c>
       <c r="H908" t="n">
         <v>54943</v>
@@ -26875,7 +26875,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G914" t="n">
-        <v>1.7864716053009</v>
+        <v>1.78647184371948</v>
       </c>
       <c r="H914" t="n">
         <v>114346</v>
@@ -26904,7 +26904,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G915" t="n">
-        <v>1.69406843185425</v>
+        <v>1.69406819343567</v>
       </c>
       <c r="H915" t="n">
         <v>74923</v>
@@ -26933,7 +26933,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G916" t="n">
-        <v>1.6786675453186</v>
+        <v>1.67866742610931</v>
       </c>
       <c r="H916" t="n">
         <v>37385</v>
@@ -26991,7 +26991,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G918" t="n">
-        <v>1.70176863670349</v>
+        <v>1.7017685174942</v>
       </c>
       <c r="H918" t="n">
         <v>6313</v>
@@ -27020,7 +27020,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G919" t="n">
-        <v>1.70946896076202</v>
+        <v>1.70946872234344</v>
       </c>
       <c r="H919" t="n">
         <v>27945</v>
@@ -27078,7 +27078,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G921" t="n">
-        <v>1.69406843185425</v>
+        <v>1.69406819343567</v>
       </c>
       <c r="H921" t="n">
         <v>9044</v>
@@ -27107,7 +27107,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G922" t="n">
-        <v>1.70176863670349</v>
+        <v>1.7017685174942</v>
       </c>
       <c r="H922" t="n">
         <v>8040</v>
@@ -27136,7 +27136,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G923" t="n">
-        <v>1.69406843185425</v>
+        <v>1.69406819343567</v>
       </c>
       <c r="H923" t="n">
         <v>50437</v>
@@ -27252,7 +27252,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G927" t="n">
-        <v>1.74026989936829</v>
+        <v>1.74027001857758</v>
       </c>
       <c r="H927" t="n">
         <v>9175</v>
@@ -27310,7 +27310,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G929" t="n">
-        <v>1.74026989936829</v>
+        <v>1.74027001857758</v>
       </c>
       <c r="H929" t="n">
         <v>16172</v>
@@ -27571,7 +27571,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G938" t="n">
-        <v>1.79417204856873</v>
+        <v>1.79417216777802</v>
       </c>
       <c r="H938" t="n">
         <v>26162</v>
@@ -27948,7 +27948,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G951" t="n">
-        <v>1.70946896076202</v>
+        <v>1.70946872234344</v>
       </c>
       <c r="H951" t="n">
         <v>17620</v>
@@ -27977,7 +27977,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G952" t="n">
-        <v>1.70176863670349</v>
+        <v>1.7017685174942</v>
       </c>
       <c r="H952" t="n">
         <v>16967</v>
@@ -28035,7 +28035,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G954" t="n">
-        <v>1.74026989936829</v>
+        <v>1.74027001857758</v>
       </c>
       <c r="H954" t="n">
         <v>9241</v>
@@ -28122,7 +28122,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G957" t="n">
-        <v>1.70176863670349</v>
+        <v>1.7017685174942</v>
       </c>
       <c r="H957" t="n">
         <v>10749</v>
@@ -28151,7 +28151,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>1.70176863670349</v>
+        <v>1.7017685174942</v>
       </c>
       <c r="H958" t="n">
         <v>11080</v>
@@ -28325,7 +28325,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G964" t="n">
-        <v>1.74026989936829</v>
+        <v>1.74027001857758</v>
       </c>
       <c r="H964" t="n">
         <v>26422</v>
@@ -28383,7 +28383,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G966" t="n">
-        <v>1.7864716053009</v>
+        <v>1.78647184371948</v>
       </c>
       <c r="H966" t="n">
         <v>21954</v>
@@ -28470,7 +28470,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G969" t="n">
-        <v>1.74026989936829</v>
+        <v>1.74027001857758</v>
       </c>
       <c r="H969" t="n">
         <v>5902</v>
@@ -28992,7 +28992,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G987" t="n">
-        <v>1.90197646617889</v>
+        <v>1.90197670459747</v>
       </c>
       <c r="H987" t="n">
         <v>22004</v>
@@ -29137,7 +29137,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G992" t="n">
-        <v>1.69406843185425</v>
+        <v>1.69406819343567</v>
       </c>
       <c r="H992" t="n">
         <v>199301</v>
@@ -29282,7 +29282,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G997" t="n">
-        <v>1.7864716053009</v>
+        <v>1.78647184371948</v>
       </c>
       <c r="H997" t="n">
         <v>52163</v>
@@ -29340,7 +29340,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G999" t="n">
-        <v>1.7864716053009</v>
+        <v>1.78647184371948</v>
       </c>
       <c r="H999" t="n">
         <v>33194</v>
@@ -29804,7 +29804,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.90197646617889</v>
+        <v>1.90197670459747</v>
       </c>
       <c r="H1015" t="n">
         <v>42293</v>
@@ -30558,7 +30558,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.70946896076202</v>
+        <v>1.70946872234344</v>
       </c>
       <c r="H1041" t="n">
         <v>72222</v>
@@ -30587,7 +30587,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.74026989936829</v>
+        <v>1.74027001857758</v>
       </c>
       <c r="H1042" t="n">
         <v>60341</v>
@@ -30877,7 +30877,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.70946896076202</v>
+        <v>1.70946872234344</v>
       </c>
       <c r="H1052" t="n">
         <v>14067</v>
@@ -30993,7 +30993,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.48615980148315</v>
+        <v>1.48615968227386</v>
       </c>
       <c r="H1056" t="n">
         <v>39239</v>
@@ -31022,7 +31022,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.42455732822418</v>
+        <v>1.42455744743347</v>
       </c>
       <c r="H1057" t="n">
         <v>39892</v>
@@ -31080,7 +31080,7 @@
         <v>1.75</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.34755432605743</v>
+        <v>1.34755420684814</v>
       </c>
       <c r="H1059" t="n">
         <v>84247</v>
@@ -31167,7 +31167,7 @@
         <v>1.60500001907349</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.23589980602264</v>
+        <v>1.23589968681335</v>
       </c>
       <c r="H1062" t="n">
         <v>198154</v>
@@ -31196,7 +31196,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.11654496192932</v>
+        <v>1.11654508113861</v>
       </c>
       <c r="H1063" t="n">
         <v>64628</v>
@@ -31225,7 +31225,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1064" t="n">
         <v>56808</v>
@@ -31283,7 +31283,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.09729421138763</v>
+        <v>1.09729409217834</v>
       </c>
       <c r="H1066" t="n">
         <v>68787</v>
@@ -31312,7 +31312,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1067" t="n">
         <v>54799</v>
@@ -31370,7 +31370,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.966388881206512</v>
+        <v>0.966389000415802</v>
       </c>
       <c r="H1069" t="n">
         <v>18734</v>
@@ -31486,7 +31486,7 @@
         <v>1.32500004768372</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.02029120922089</v>
+        <v>1.0202910900116</v>
       </c>
       <c r="H1073" t="n">
         <v>15024</v>
@@ -31515,7 +31515,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.10114443302155</v>
+        <v>1.10114431381226</v>
       </c>
       <c r="H1074" t="n">
         <v>22278</v>
@@ -31573,7 +31573,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.12039506435394</v>
+        <v>1.12039518356323</v>
       </c>
       <c r="H1076" t="n">
         <v>24001</v>
@@ -31689,7 +31689,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.10114443302155</v>
+        <v>1.10114431381226</v>
       </c>
       <c r="H1080" t="n">
         <v>3640</v>
@@ -31718,7 +31718,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.10114443302155</v>
+        <v>1.10114431381226</v>
       </c>
       <c r="H1081" t="n">
         <v>4000</v>
@@ -32008,7 +32008,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.14734613895416</v>
+        <v>1.14734625816345</v>
       </c>
       <c r="H1091" t="n">
         <v>18852</v>
@@ -32037,7 +32037,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.11654496192932</v>
+        <v>1.11654508113861</v>
       </c>
       <c r="H1092" t="n">
         <v>8234</v>
@@ -32124,7 +32124,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.11654496192932</v>
+        <v>1.11654508113861</v>
       </c>
       <c r="H1095" t="n">
         <v>9238</v>
@@ -32211,7 +32211,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.11654496192932</v>
+        <v>1.11654508113861</v>
       </c>
       <c r="H1098" t="n">
         <v>56840</v>
@@ -32269,7 +32269,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.0664929151535</v>
+        <v>1.06649279594421</v>
       </c>
       <c r="H1100" t="n">
         <v>4984</v>
@@ -32298,7 +32298,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.10114443302155</v>
+        <v>1.10114431381226</v>
       </c>
       <c r="H1101" t="n">
         <v>4360</v>
@@ -32327,7 +32327,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.10114443302155</v>
+        <v>1.10114431381226</v>
       </c>
       <c r="H1102" t="n">
         <v>620</v>
@@ -32443,7 +32443,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.10114443302155</v>
+        <v>1.10114431381226</v>
       </c>
       <c r="H1106" t="n">
         <v>5939</v>
@@ -32617,7 +32617,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.0664929151535</v>
+        <v>1.06649279594421</v>
       </c>
       <c r="H1112" t="n">
         <v>9315</v>
@@ -32675,7 +32675,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.0664929151535</v>
+        <v>1.06649279594421</v>
       </c>
       <c r="H1114" t="n">
         <v>4011</v>
@@ -32849,7 +32849,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.09729421138763</v>
+        <v>1.09729409217834</v>
       </c>
       <c r="H1120" t="n">
         <v>29557</v>
@@ -32878,7 +32878,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1121" t="n">
         <v>45952</v>
@@ -33081,7 +33081,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1128" t="n">
         <v>43440</v>
@@ -33110,7 +33110,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.12039506435394</v>
+        <v>1.12039518356323</v>
       </c>
       <c r="H1129" t="n">
         <v>22720</v>
@@ -33139,7 +33139,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.12039506435394</v>
+        <v>1.12039518356323</v>
       </c>
       <c r="H1130" t="n">
         <v>13597</v>
@@ -33255,7 +33255,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.14734613895416</v>
+        <v>1.14734625816345</v>
       </c>
       <c r="H1134" t="n">
         <v>4014</v>
@@ -33313,7 +33313,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.14734613895416</v>
+        <v>1.14734625816345</v>
       </c>
       <c r="H1136" t="n">
         <v>2027</v>
@@ -33429,7 +33429,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.11654496192932</v>
+        <v>1.11654508113861</v>
       </c>
       <c r="H1140" t="n">
         <v>6790</v>
@@ -33458,7 +33458,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1141" t="n">
         <v>1193</v>
@@ -33574,7 +33574,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.12039506435394</v>
+        <v>1.12039518356323</v>
       </c>
       <c r="H1145" t="n">
         <v>3500</v>
@@ -33603,7 +33603,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.12039506435394</v>
+        <v>1.12039518356323</v>
       </c>
       <c r="H1146" t="n">
         <v>2600</v>
@@ -33777,7 +33777,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1152" t="n">
         <v>13107</v>
@@ -33980,7 +33980,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1159" t="n">
         <v>32762</v>
@@ -34009,7 +34009,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.12039506435394</v>
+        <v>1.12039518356323</v>
       </c>
       <c r="H1160" t="n">
         <v>1555</v>
@@ -34038,7 +34038,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.12039506435394</v>
+        <v>1.12039518356323</v>
       </c>
       <c r="H1161" t="n">
         <v>1150</v>
@@ -34299,7 +34299,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.0664929151535</v>
+        <v>1.06649279594421</v>
       </c>
       <c r="H1170" t="n">
         <v>2627</v>
@@ -34531,7 +34531,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.0664929151535</v>
+        <v>1.06649279594421</v>
       </c>
       <c r="H1178" t="n">
         <v>3686</v>
@@ -34647,7 +34647,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.0664929151535</v>
+        <v>1.06649279594421</v>
       </c>
       <c r="H1182" t="n">
         <v>9317</v>
@@ -34792,7 +34792,7 @@
         <v>1.38499999046326</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.0664929151535</v>
+        <v>1.06649279594421</v>
       </c>
       <c r="H1187" t="n">
         <v>56180</v>
@@ -35024,7 +35024,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.11654496192932</v>
+        <v>1.11654508113861</v>
       </c>
       <c r="H1195" t="n">
         <v>33474</v>
@@ -35053,7 +35053,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.09729421138763</v>
+        <v>1.09729409217834</v>
       </c>
       <c r="H1196" t="n">
         <v>6716</v>
@@ -35372,7 +35372,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.02414131164551</v>
+        <v>1.02414119243622</v>
       </c>
       <c r="H1207" t="n">
         <v>11046</v>
@@ -35401,7 +35401,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.02414131164551</v>
+        <v>1.02414119243622</v>
       </c>
       <c r="H1208" t="n">
         <v>14952</v>
@@ -35488,7 +35488,7 @@
         <v>1.33000004291534</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.02414131164551</v>
+        <v>1.02414119243622</v>
       </c>
       <c r="H1211" t="n">
         <v>6550</v>
@@ -35749,7 +35749,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1220" t="n">
-        <v>0.974089205265045</v>
+        <v>0.974089324474335</v>
       </c>
       <c r="H1220" t="n">
         <v>12007</v>
@@ -35778,7 +35778,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1221" t="n">
-        <v>0.977939307689667</v>
+        <v>0.977939426898956</v>
       </c>
       <c r="H1221" t="n">
         <v>22788</v>
@@ -35807,7 +35807,7 @@
         <v>1.24000000953674</v>
       </c>
       <c r="G1222" t="n">
-        <v>0.954838395118713</v>
+        <v>0.954838514328003</v>
       </c>
       <c r="H1222" t="n">
         <v>45000</v>
@@ -35981,7 +35981,7 @@
         <v>1.25</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.962538778781891</v>
+        <v>0.962538838386536</v>
       </c>
       <c r="H1228" t="n">
         <v>124772</v>
@@ -36184,7 +36184,7 @@
         <v>1.25999999046326</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.970238983631134</v>
+        <v>0.970239102840424</v>
       </c>
       <c r="H1235" t="n">
         <v>147511</v>
@@ -36358,7 +36358,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1241" t="n">
         <v>132253</v>
@@ -36387,7 +36387,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.17429721355438</v>
+        <v>1.17429733276367</v>
       </c>
       <c r="H1242" t="n">
         <v>103238</v>
@@ -36416,7 +36416,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1243" t="n">
         <v>29500</v>
@@ -36445,7 +36445,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.11654496192932</v>
+        <v>1.11654508113861</v>
       </c>
       <c r="H1244" t="n">
         <v>120564</v>
@@ -36474,7 +36474,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.11654496192932</v>
+        <v>1.11654508113861</v>
       </c>
       <c r="H1245" t="n">
         <v>44365</v>
@@ -36648,7 +36648,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.09729421138763</v>
+        <v>1.09729409217834</v>
       </c>
       <c r="H1251" t="n">
         <v>36917</v>
@@ -36880,7 +36880,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.17429721355438</v>
+        <v>1.17429733276367</v>
       </c>
       <c r="H1259" t="n">
         <v>5538</v>
@@ -36996,7 +36996,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.14734613895416</v>
+        <v>1.14734625816345</v>
       </c>
       <c r="H1263" t="n">
         <v>28061</v>
@@ -37257,7 +37257,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1272" t="n">
         <v>11286</v>
@@ -37286,7 +37286,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.14734613895416</v>
+        <v>1.14734625816345</v>
       </c>
       <c r="H1273" t="n">
         <v>2876</v>
@@ -37373,7 +37373,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.14734613895416</v>
+        <v>1.14734625816345</v>
       </c>
       <c r="H1276" t="n">
         <v>27445</v>
@@ -37402,7 +37402,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.14349591732025</v>
+        <v>1.14349603652954</v>
       </c>
       <c r="H1277" t="n">
         <v>10683</v>
@@ -37431,7 +37431,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.14349591732025</v>
+        <v>1.14349603652954</v>
       </c>
       <c r="H1278" t="n">
         <v>2270</v>
@@ -37460,7 +37460,7 @@
         <v>1.49000000953674</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.14734613895416</v>
+        <v>1.14734625816345</v>
       </c>
       <c r="H1279" t="n">
         <v>1000</v>
@@ -37518,7 +37518,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1281" t="n">
         <v>1036</v>
@@ -37576,7 +37576,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1283" t="n">
         <v>3730</v>
@@ -37663,7 +37663,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1286" t="n">
-        <v>1.11654496192932</v>
+        <v>1.11654508113861</v>
       </c>
       <c r="H1286" t="n">
         <v>14988</v>
@@ -37721,7 +37721,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.09729421138763</v>
+        <v>1.09729409217834</v>
       </c>
       <c r="H1288" t="n">
         <v>10803</v>
@@ -37866,7 +37866,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.10114443302155</v>
+        <v>1.10114431381226</v>
       </c>
       <c r="H1293" t="n">
         <v>13436</v>
@@ -37924,7 +37924,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1295" t="n">
-        <v>1.10114443302155</v>
+        <v>1.10114431381226</v>
       </c>
       <c r="H1295" t="n">
         <v>42043</v>
@@ -38040,7 +38040,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.11654496192932</v>
+        <v>1.11654508113861</v>
       </c>
       <c r="H1299" t="n">
         <v>53814</v>
@@ -38127,7 +38127,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.12039506435394</v>
+        <v>1.12039518356323</v>
       </c>
       <c r="H1302" t="n">
         <v>31199</v>
@@ -38243,7 +38243,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1306" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1306" t="n">
         <v>1875</v>
@@ -38272,7 +38272,7 @@
         <v>1.42999994754791</v>
       </c>
       <c r="G1307" t="n">
-        <v>1.10114443302155</v>
+        <v>1.10114431381226</v>
       </c>
       <c r="H1307" t="n">
         <v>8880</v>
@@ -38330,7 +38330,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.13964581489563</v>
+        <v>1.13964593410492</v>
       </c>
       <c r="H1309" t="n">
         <v>191557</v>
@@ -38446,7 +38446,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.17429721355438</v>
+        <v>1.17429733276367</v>
       </c>
       <c r="H1313" t="n">
         <v>40172</v>
@@ -38620,7 +38620,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.26285076141357</v>
+        <v>1.26285064220428</v>
       </c>
       <c r="H1319" t="n">
         <v>15461</v>
@@ -38678,7 +38678,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.2705512046814</v>
+        <v>1.27055108547211</v>
       </c>
       <c r="H1321" t="n">
         <v>52734</v>
@@ -38736,7 +38736,7 @@
         <v>1.75</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.34755432605743</v>
+        <v>1.34755420684814</v>
       </c>
       <c r="H1323" t="n">
         <v>51442</v>
@@ -38794,7 +38794,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1325" t="n">
         <v>66175</v>
@@ -39142,7 +39142,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.43225765228271</v>
+        <v>1.43225753307343</v>
       </c>
       <c r="H1337" t="n">
         <v>81573</v>
@@ -39229,7 +39229,7 @@
         <v>1.875</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.44380819797516</v>
+        <v>1.44380807876587</v>
       </c>
       <c r="H1340" t="n">
         <v>17050</v>
@@ -39345,7 +39345,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.51311099529266</v>
+        <v>1.51311087608337</v>
       </c>
       <c r="H1344" t="n">
         <v>47221</v>
@@ -39374,7 +39374,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.48615980148315</v>
+        <v>1.48615968227386</v>
       </c>
       <c r="H1345" t="n">
         <v>58184</v>
@@ -39577,7 +39577,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.4284074306488</v>
+        <v>1.42840731143951</v>
       </c>
       <c r="H1352" t="n">
         <v>60068</v>
@@ -39606,7 +39606,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.4284074306488</v>
+        <v>1.42840731143951</v>
       </c>
       <c r="H1353" t="n">
         <v>101165</v>
@@ -39983,7 +39983,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1366" t="n">
         <v>7655</v>
@@ -40070,7 +40070,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1369" t="n">
         <v>21253</v>
@@ -40186,7 +40186,7 @@
         <v>1.875</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.44380819797516</v>
+        <v>1.44380807876587</v>
       </c>
       <c r="H1373" t="n">
         <v>12713</v>
@@ -40505,7 +40505,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.64016628265381</v>
+        <v>1.64016616344452</v>
       </c>
       <c r="H1384" t="n">
         <v>74760</v>
@@ -40592,7 +40592,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.53621172904968</v>
+        <v>1.53621184825897</v>
       </c>
       <c r="H1387" t="n">
         <v>170541</v>
@@ -40737,7 +40737,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1392" t="n">
         <v>20411</v>
@@ -40766,7 +40766,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1393" t="n">
         <v>7843</v>
@@ -40795,7 +40795,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1394" t="n">
         <v>12739</v>
@@ -40824,7 +40824,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1395" t="n">
         <v>10614</v>
@@ -40853,7 +40853,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1396" t="n">
         <v>82912</v>
@@ -41375,7 +41375,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.6324657201767</v>
+        <v>1.63246560096741</v>
       </c>
       <c r="H1414" t="n">
         <v>5198</v>
@@ -41404,7 +41404,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.6786675453186</v>
+        <v>1.67866742610931</v>
       </c>
       <c r="H1415" t="n">
         <v>137084</v>
@@ -41578,7 +41578,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.69406843185425</v>
+        <v>1.69406819343567</v>
       </c>
       <c r="H1421" t="n">
         <v>62263</v>
@@ -41607,7 +41607,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.6786675453186</v>
+        <v>1.67866742610931</v>
       </c>
       <c r="H1422" t="n">
         <v>82507</v>
@@ -41723,7 +41723,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.64016628265381</v>
+        <v>1.64016616344452</v>
       </c>
       <c r="H1426" t="n">
         <v>3897</v>
@@ -41752,7 +41752,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.64016628265381</v>
+        <v>1.64016616344452</v>
       </c>
       <c r="H1427" t="n">
         <v>1076</v>
@@ -41781,7 +41781,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.64016628265381</v>
+        <v>1.64016616344452</v>
       </c>
       <c r="H1428" t="n">
         <v>0</v>
@@ -41810,7 +41810,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.64016628265381</v>
+        <v>1.64016616344452</v>
       </c>
       <c r="H1429" t="n">
         <v>2996</v>
@@ -41839,7 +41839,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.6324657201767</v>
+        <v>1.63246560096741</v>
       </c>
       <c r="H1430" t="n">
         <v>11218</v>
@@ -41868,7 +41868,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.6324657201767</v>
+        <v>1.63246560096741</v>
       </c>
       <c r="H1431" t="n">
         <v>4382</v>
@@ -41984,7 +41984,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.6324657201767</v>
+        <v>1.63246560096741</v>
       </c>
       <c r="H1435" t="n">
         <v>4842</v>
@@ -42274,7 +42274,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.53621172904968</v>
+        <v>1.53621184825897</v>
       </c>
       <c r="H1445" t="n">
         <v>152241</v>
@@ -42303,7 +42303,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.53621172904968</v>
+        <v>1.53621184825897</v>
       </c>
       <c r="H1446" t="n">
         <v>23522</v>
@@ -42448,7 +42448,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1451" t="n">
         <v>12601</v>
@@ -42535,7 +42535,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1454" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1454" t="n">
         <v>11141</v>
@@ -42651,7 +42651,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1458" t="n">
         <v>8407</v>
@@ -42825,7 +42825,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1464" t="n">
-        <v>1.43225765228271</v>
+        <v>1.43225753307343</v>
       </c>
       <c r="H1464" t="n">
         <v>13265</v>
@@ -42854,7 +42854,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.43225765228271</v>
+        <v>1.43225753307343</v>
       </c>
       <c r="H1465" t="n">
         <v>500</v>
@@ -43115,7 +43115,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1474" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1474" t="n">
         <v>12445</v>
@@ -43144,7 +43144,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1475" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1475" t="n">
         <v>4690</v>
@@ -43434,7 +43434,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1485" t="n">
-        <v>1.48615980148315</v>
+        <v>1.48615968227386</v>
       </c>
       <c r="H1485" t="n">
         <v>12224</v>
@@ -43463,7 +43463,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1486" t="n">
-        <v>1.43225765228271</v>
+        <v>1.43225753307343</v>
       </c>
       <c r="H1486" t="n">
         <v>69361</v>
@@ -43492,7 +43492,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1487" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1487" t="n">
         <v>11488</v>
@@ -43521,7 +43521,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1488" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1488" t="n">
         <v>26124</v>
@@ -43724,7 +43724,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1495" t="n">
-        <v>1.48230957984924</v>
+        <v>1.48230946063995</v>
       </c>
       <c r="H1495" t="n">
         <v>23148</v>
@@ -43956,7 +43956,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1503" t="n">
-        <v>1.43225765228271</v>
+        <v>1.43225753307343</v>
       </c>
       <c r="H1503" t="n">
         <v>38958</v>
@@ -44014,7 +44014,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1505" t="n">
-        <v>1.4284074306488</v>
+        <v>1.42840731143951</v>
       </c>
       <c r="H1505" t="n">
         <v>5501</v>
@@ -44043,7 +44043,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1506" t="n">
-        <v>1.43225765228271</v>
+        <v>1.43225753307343</v>
       </c>
       <c r="H1506" t="n">
         <v>722</v>
@@ -44130,7 +44130,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1509" t="n">
-        <v>1.4284074306488</v>
+        <v>1.42840731143951</v>
       </c>
       <c r="H1509" t="n">
         <v>4666</v>
@@ -44159,7 +44159,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1510" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1510" t="n">
         <v>4933</v>
@@ -44188,7 +44188,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1511" t="n">
-        <v>1.42070722579956</v>
+        <v>1.42070734500885</v>
       </c>
       <c r="H1511" t="n">
         <v>4715</v>
@@ -44362,7 +44362,7 @@
         <v>1.875</v>
       </c>
       <c r="G1517" t="n">
-        <v>1.44380819797516</v>
+        <v>1.44380807876587</v>
       </c>
       <c r="H1517" t="n">
         <v>11316</v>
@@ -44391,7 +44391,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1518" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1518" t="n">
         <v>1334</v>
@@ -44420,7 +44420,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1519" t="n">
-        <v>1.42455732822418</v>
+        <v>1.42455744743347</v>
       </c>
       <c r="H1519" t="n">
         <v>4005</v>
@@ -44449,7 +44449,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1520" t="n">
-        <v>1.4284074306488</v>
+        <v>1.42840731143951</v>
       </c>
       <c r="H1520" t="n">
         <v>706</v>
@@ -44478,7 +44478,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1521" t="n">
-        <v>1.4284074306488</v>
+        <v>1.42840731143951</v>
       </c>
       <c r="H1521" t="n">
         <v>8392</v>
@@ -44507,7 +44507,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1522" t="n">
-        <v>1.43225765228271</v>
+        <v>1.43225753307343</v>
       </c>
       <c r="H1522" t="n">
         <v>4939</v>
@@ -44623,7 +44623,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1526" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1526" t="n">
         <v>3949</v>
@@ -44710,7 +44710,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1529" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1529" t="n">
         <v>12453</v>
@@ -44739,7 +44739,7 @@
         <v>1.875</v>
       </c>
       <c r="G1530" t="n">
-        <v>1.44380819797516</v>
+        <v>1.44380807876587</v>
       </c>
       <c r="H1530" t="n">
         <v>23084</v>
@@ -44768,7 +44768,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1531" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1531" t="n">
         <v>13603</v>
@@ -44797,7 +44797,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1532" t="n">
-        <v>1.4284074306488</v>
+        <v>1.42840731143951</v>
       </c>
       <c r="H1532" t="n">
         <v>9500</v>
@@ -44855,7 +44855,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1534" t="n">
-        <v>1.48230957984924</v>
+        <v>1.48230946063995</v>
       </c>
       <c r="H1534" t="n">
         <v>136576</v>
@@ -44942,7 +44942,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1537" t="n">
-        <v>1.51696121692657</v>
+        <v>1.51696109771729</v>
       </c>
       <c r="H1537" t="n">
         <v>79316</v>
@@ -45116,7 +45116,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1543" t="n">
-        <v>1.42455732822418</v>
+        <v>1.42455744743347</v>
       </c>
       <c r="H1543" t="n">
         <v>8121</v>
@@ -45232,7 +45232,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1547" t="n">
-        <v>1.43610787391663</v>
+        <v>1.43610775470734</v>
       </c>
       <c r="H1547" t="n">
         <v>8780</v>
@@ -45435,7 +45435,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1554" t="n">
-        <v>1.53621172904968</v>
+        <v>1.53621184825897</v>
       </c>
       <c r="H1554" t="n">
         <v>57339</v>
@@ -45464,7 +45464,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1555" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1555" t="n">
         <v>60473</v>
@@ -45580,7 +45580,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1559" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1559" t="n">
         <v>30415</v>
@@ -45725,7 +45725,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1564" t="n">
-        <v>1.51311099529266</v>
+        <v>1.51311087608337</v>
       </c>
       <c r="H1564" t="n">
         <v>4794</v>
@@ -45754,7 +45754,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.42455732822418</v>
+        <v>1.42455744743347</v>
       </c>
       <c r="H1565" t="n">
         <v>28003</v>
@@ -45783,7 +45783,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1566" t="n">
-        <v>1.4284074306488</v>
+        <v>1.42840731143951</v>
       </c>
       <c r="H1566" t="n">
         <v>523</v>
@@ -45812,7 +45812,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.48230957984924</v>
+        <v>1.48230946063995</v>
       </c>
       <c r="H1567" t="n">
         <v>13493</v>
@@ -45841,7 +45841,7 @@
         <v>1.875</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.44380819797516</v>
+        <v>1.44380807876587</v>
       </c>
       <c r="H1568" t="n">
         <v>7560</v>
@@ -45899,7 +45899,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1570" t="n">
-        <v>1.42455732822418</v>
+        <v>1.42455744743347</v>
       </c>
       <c r="H1570" t="n">
         <v>2162</v>
@@ -46247,7 +46247,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.39375603199005</v>
+        <v>1.39375615119934</v>
       </c>
       <c r="H1582" t="n">
         <v>22901</v>
@@ -46363,7 +46363,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1586" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1586" t="n">
         <v>8314</v>
@@ -46421,7 +46421,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1588" t="n">
-        <v>1.43995797634125</v>
+        <v>1.43995785713196</v>
       </c>
       <c r="H1588" t="n">
         <v>4930</v>
@@ -46450,7 +46450,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.43610787391663</v>
+        <v>1.43610775470734</v>
       </c>
       <c r="H1589" t="n">
         <v>2138</v>
@@ -46479,7 +46479,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.4284074306488</v>
+        <v>1.42840731143951</v>
       </c>
       <c r="H1590" t="n">
         <v>8192</v>
@@ -46508,7 +46508,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.43225765228271</v>
+        <v>1.43225753307343</v>
       </c>
       <c r="H1591" t="n">
         <v>5602</v>
@@ -46537,7 +46537,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.43225765228271</v>
+        <v>1.43225753307343</v>
       </c>
       <c r="H1592" t="n">
         <v>10057</v>
@@ -47117,7 +47117,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G1612" t="n">
-        <v>1.52081143856049</v>
+        <v>1.5208113193512</v>
       </c>
       <c r="H1612" t="n">
         <v>7744</v>
@@ -47407,7 +47407,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1622" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1622" t="n">
         <v>156</v>
@@ -47436,7 +47436,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1623" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1623" t="n">
         <v>25969</v>
@@ -47610,7 +47610,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1629" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1629" t="n">
         <v>11865</v>
@@ -47639,7 +47639,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1630" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1630" t="n">
         <v>9864</v>
@@ -47668,7 +47668,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1631" t="n">
         <v>4133</v>
@@ -47697,7 +47697,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1632" t="n">
         <v>2311</v>
@@ -47726,7 +47726,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.5631628036499</v>
+        <v>1.56316292285919</v>
       </c>
       <c r="H1633" t="n">
         <v>9274</v>
@@ -48016,7 +48016,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1643" t="n">
-        <v>1.53621172904968</v>
+        <v>1.53621184825897</v>
       </c>
       <c r="H1643" t="n">
         <v>896</v>
@@ -48219,7 +48219,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1650" t="n">
-        <v>1.4284074306488</v>
+        <v>1.42840731143951</v>
       </c>
       <c r="H1650" t="n">
         <v>9476</v>
@@ -48393,7 +48393,7 @@
         <v>1.9650000333786</v>
       </c>
       <c r="G1656" t="n">
-        <v>1.51311099529266</v>
+        <v>1.51311087608337</v>
       </c>
       <c r="H1656" t="n">
         <v>12158</v>
@@ -48480,7 +48480,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1659" t="n">
-        <v>1.53236162662506</v>
+        <v>1.53236174583435</v>
       </c>
       <c r="H1659" t="n">
         <v>8359</v>
@@ -79951,6 +79951,64 @@
         <v>15894</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>2.40000009536743</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>17148</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>2.38000011444092</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>2.26999998092651</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>2.34999990463257</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>20124</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>
